--- a/docs/xlsx/jobs-2026-09-18.xlsx
+++ b/docs/xlsx/jobs-2026-09-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="540">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1609 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>1700 Hour Community Tree Steward</t>
+  </si>
+  <si>
+    <t>Maine Conservation Corps</t>
+  </si>
+  <si>
+    <t>Augusta, ME</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$680 per week</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-1700-hour-community-tree-steward-augusta-maine/8542491592</t>
+  </si>
+  <si>
+    <t>1700 Hour Environmental Steward</t>
+  </si>
+  <si>
+    <t>$535 per week</t>
+  </si>
+  <si>
+    <t>botany-ecology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-1700-hour-environmental-steward-augusta-maine/2400716952</t>
+  </si>
+  <si>
+    <t>Angelina-Sabine National Forest Prescribed Fire Corps Leader</t>
+  </si>
+  <si>
+    <t>Student Conservation Association</t>
+  </si>
+  <si>
+    <t>Zavalla, TX</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$850 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-angelina-sabine-national-forest-prescribed-fire-corps-leader-zavalla-texas/9045929294</t>
+  </si>
+  <si>
+    <t>Assistant Professor of Silviculture</t>
+  </si>
+  <si>
+    <t>University of Montana Department of Forest Management</t>
+  </si>
+  <si>
+    <t>Missoula, MT</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$70,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-professor-of-silviculture-missoula-montana/4285576148</t>
+  </si>
+  <si>
+    <t>Associate Director</t>
+  </si>
+  <si>
+    <t>Archbold Expeditions Inc</t>
+  </si>
+  <si>
+    <t>Venus, FL</t>
+  </si>
+  <si>
+    <t>$100,000 - $120,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-director-venus-florida/5321283170</t>
+  </si>
+  <si>
+    <t>Conservation Technician</t>
+  </si>
+  <si>
+    <t>Schoolcraft Conservation District</t>
+  </si>
+  <si>
+    <t>Manistique, MI</t>
+  </si>
+  <si>
+    <t>$22 - $25 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-technician-manistique-michigan/7739142723</t>
+  </si>
+  <si>
+    <t>Director or Senior Director of Government Relations, New York State</t>
+  </si>
+  <si>
+    <t>Open Space Institute</t>
+  </si>
+  <si>
+    <t>Albany, NY</t>
+  </si>
+  <si>
+    <t>$140,000 - $190,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-or-senior-director-of-government-relations-new-york-state-albany-new-york/5428875683</t>
+  </si>
+  <si>
+    <t>Education Manager, Academy of Rescue &amp; Conservation</t>
+  </si>
+  <si>
+    <t>The International Fund for Animal Welfare</t>
+  </si>
+  <si>
+    <t>United States, Remote</t>
+  </si>
+  <si>
+    <t>$80,000 - $100,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-education-manager-academy-of-rescue--conservation-united-states-remote/2935072650</t>
+  </si>
+  <si>
+    <t>Environmental Scientist</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>$4,418 - $9,321 per month</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-scientist-los-angeles-california/2853489901</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Vermont Center for Ecostudies</t>
+  </si>
+  <si>
+    <t>White River Junction, VT</t>
+  </si>
+  <si>
+    <t>$150,000 - $225,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-executive-director-white-river-junction-vermont/8182039665</t>
+  </si>
+  <si>
+    <t>GIS Analyst III</t>
+  </si>
+  <si>
+    <t>Idaho Department of Fish and Game</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>$36.16 - $45.20 per hour</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-gis-analyst-iii-boise-idaho/9909761871</t>
+  </si>
+  <si>
+    <t>HAWKs Educator</t>
+  </si>
+  <si>
+    <t>HAWKs Crescenta Valley</t>
+  </si>
+  <si>
+    <t>$25 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hawks-educator-los-angeles-california/5648006008</t>
+  </si>
+  <si>
+    <t>Jill Abrahamson Memorial Environmental Education Fellowship</t>
+  </si>
+  <si>
+    <t>Archbold</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$15 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-jill-abrahamson-memorial-environmental-education-fellowship-venus-florida/1785440833</t>
+  </si>
+  <si>
+    <t>Natural Resources Planner</t>
+  </si>
+  <si>
+    <t>Rutland Natural Resources Conservation District</t>
+  </si>
+  <si>
+    <t>Rutland, VT</t>
+  </si>
+  <si>
+    <t>$23 - $25 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-planner-rutland-vermont/3103718589</t>
+  </si>
+  <si>
+    <t>President and CEO</t>
+  </si>
+  <si>
+    <t>Schoodic Institute at Acadia National Park</t>
+  </si>
+  <si>
+    <t>Winter Harbor, ME</t>
+  </si>
+  <si>
+    <t>$150,000 - $200,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-president-and-ceo-winter-harbor-maine/5619755362</t>
+  </si>
+  <si>
+    <t>Program Analyst</t>
+  </si>
+  <si>
+    <t>Watershed Stewards Program</t>
+  </si>
+  <si>
+    <t>San Luis Obispo, CA</t>
+  </si>
+  <si>
+    <t>$3,861 - $6,276 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-analyst-san-luis-obispo-california/2332389969</t>
+  </si>
+  <si>
+    <t>Program Specialist- Bison Operations</t>
+  </si>
+  <si>
+    <t>American Prairie</t>
+  </si>
+  <si>
+    <t>Malta, MT</t>
+  </si>
+  <si>
+    <t>$20.75 - $23 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-specialist--bison-operations-malta-montana/9219243375</t>
+  </si>
+  <si>
+    <t>Public Lands Fellow</t>
+  </si>
+  <si>
+    <t>Oregon Wild</t>
+  </si>
+  <si>
+    <t>Portland (Preferred) or Bend, OR</t>
+  </si>
+  <si>
+    <t>$60,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-public-lands-fellow-portland-preferred-or-bend-oregon/1895786462</t>
+  </si>
+  <si>
+    <t>Region 8 Prescribed Fire Corps Leader</t>
+  </si>
+  <si>
+    <t>Atlanta, GA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-region-8-prescribedfirecorps-leader-atlanta-georgia/9033636149</t>
+  </si>
+  <si>
+    <t>Region Director of Philanthropy - California</t>
+  </si>
+  <si>
+    <t>Trust for Public Land</t>
+  </si>
+  <si>
+    <t>$165,000 - $175,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-region-director-of-philanthropy---california-los-angeles-california/5937521239</t>
+  </si>
+  <si>
+    <t>Rural Fire Program Coordinator</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>Grand Rapids, MN</t>
+  </si>
+  <si>
+    <t>$32.97 - $48.60 / hourly; $68,841 - $101,476 / annually</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-rural-fire-program-coordinator-grand-rapids-minnesota/4562883139</t>
+  </si>
+  <si>
+    <t>Sam Houston National Forest Prescribed Fire Corps Leader</t>
+  </si>
+  <si>
+    <t>New Waverly, TX</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sam-houston-national-forest-prescribedfirecorps-leader-new-waverly-texas/3761545813</t>
+  </si>
+  <si>
+    <t>School Programs Manager</t>
+  </si>
+  <si>
+    <t>North Carolina Zoo</t>
+  </si>
+  <si>
+    <t>Asheboro, NC</t>
+  </si>
+  <si>
+    <t>$37,377 - $51,500 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-school-programs-manager-asheboro-north-carolina/5749691140</t>
+  </si>
+  <si>
+    <t>Senior Program Manager - Tennessee Urban Programs</t>
+  </si>
+  <si>
+    <t>Chattanooga, TN</t>
+  </si>
+  <si>
+    <t>$91,000 - $105,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-program-manager---tennessee-urban-programs-chattanooga-tennessee/1329402220</t>
+  </si>
+  <si>
+    <t>STEM Career Pathway Support Specialist Individual Placement</t>
+  </si>
+  <si>
+    <t>Conservation Corps New Mexico</t>
+  </si>
+  <si>
+    <t>Silver City, NM</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-stem-career-pathway-support-specialist-individual-placement-silver-city-new-mexico/9299698369</t>
+  </si>
+  <si>
+    <t>Table Rock Fire Crew Leader</t>
+  </si>
+  <si>
+    <t>Clemson, SC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-table-rock-fire-crew-leader-clemson-south-carolina/3481519901</t>
+  </si>
+  <si>
+    <t>Water Resource Control Engineer</t>
+  </si>
+  <si>
+    <t>$6,488 - $12,152 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resource-control-engineer-los-angeles-california/5589555500</t>
+  </si>
+  <si>
+    <t>Watershed Restoration Specialist</t>
+  </si>
+  <si>
+    <t>South Washington Watershed District</t>
+  </si>
+  <si>
+    <t>Woodbury, MN</t>
+  </si>
+  <si>
+    <t>$68,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-restoration-specialist-woodbury-minnesota/1030647392</t>
+  </si>
+  <si>
+    <t>Wildlife Veterinary Assistant</t>
+  </si>
+  <si>
+    <t>Rainforest Awareness Rescue Education Center - RAREC</t>
+  </si>
+  <si>
+    <t>Iquitos, Lima, Peru, Latin America</t>
+  </si>
+  <si>
+    <t>3 meals per day and accommodations on-site covered, free use of laundry room, wifi and other services</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-veterinary-assistant-iquitos-latin-america/1310700255</t>
+  </si>
+  <si>
+    <t>Associate, Federal &amp; External Affairs, U.S. Climate Alliance</t>
+  </si>
+  <si>
+    <t>United Nations Foundation</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Climate Change</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/associate-federal-external-affairs-u-s-climate-alliance/</t>
+  </si>
+  <si>
+    <t>Sr. Conservation Manager, Conservation Campaigns</t>
+  </si>
+  <si>
+    <t>The Wilderness Society</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>80,000 - 100,000</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/sr-conservation-manager-conservation-campaigns/</t>
+  </si>
+  <si>
+    <t>21st Century Site Coordinator [PS 093]</t>
+  </si>
+  <si>
+    <t>Replications, Inc</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b31f727303a24464a51559b54b8c6b24-21st-century-site-coordinator-ps-093-replications-inc-brooklyn</t>
+  </si>
+  <si>
+    <t>Academic Support Specialist</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27fca777d5754387819f749424fe70d8-academic-support-specialist-replications-inc-bronx-county</t>
+  </si>
+  <si>
+    <t>Administrative Assistant – Cary Institute of Ecosystem Studies</t>
+  </si>
+  <si>
+    <t>Cary Institute of Ecosystem Studies</t>
+  </si>
+  <si>
+    <t>Millbrook, New York</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Research Social Science, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5630e83fab9646fb827d20af8f586904-administrative-assistant-cary-institute-of-ecosystem-studies-cary-institute-of-ecosystem-studies-millbrook</t>
+  </si>
+  <si>
+    <t>Administrative Operations Manager</t>
+  </si>
+  <si>
+    <t>Lift Louisiana, a project of Tides Center</t>
+  </si>
+  <si>
+    <t>New Orleans, LA</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68c0903a2fe941dc9c45b41faf7a97b2-administrative-operations-manager-lift-louisiana-a-project-of-tides-center-new-orleans</t>
+  </si>
+  <si>
+    <t>Analytics Engineer</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 128294.00 - 128294.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b6ed204559de4a74a3302180e0bff6a1-analytics-engineer-american-civil-liberties-union-washington</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a3a60492f6a54534a3c63acff62a7b51-analytics-engineer-american-civil-liberties-union-san-francisco</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/19937276c8ce4ea39b675f60ab7ba4bd-analytics-engineer-american-civil-liberties-union-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Vice President, Business Development &amp; Industry Engagement</t>
+  </si>
+  <si>
+    <t>Society for Maternal-Fetal Medicine</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e37a84afc01c40a295d15618f1270f8c-assistant-vice-president-business-development-industry-engagement-society-for-maternal-fetal-medicine-washington</t>
+  </si>
+  <si>
+    <t>Assistant, Associate, or Full Professor (Tenure-track or Tenure) - Architecture and Urban AI</t>
+  </si>
+  <si>
+    <t>CUNY School of Professional Studies</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 89777.00 - 112841.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/773a8d42492e41c5a3236aadad0484eb-assistant-associate-or-full-professor-tenure-track-or-tenure-architecture-and-urban-ai-cuny-school-of-professional-studies-new-york</t>
+  </si>
+  <si>
+    <t>Assistente de Projetos Sociais Júnior</t>
+  </si>
+  <si>
+    <t>Plan International Brasil</t>
+  </si>
+  <si>
+    <t>São Paulo, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>BRL 2520.00 - 2520.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b8e574ec2e1049f3b708305474896773-assistente-de-projetos-sociais-junior-plan-international-brasil-sao-paulo</t>
+  </si>
+  <si>
+    <t>Assistente Social</t>
+  </si>
+  <si>
+    <t>Codó, Maranhão, BR</t>
+  </si>
+  <si>
+    <t>BRL 3000.00 - 3000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Climate Change, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f81de98bd80e4773a917492734abca56-assistente-social-plan-international-brasil-codo</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, International Relations</t>
+  </si>
+  <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/209b6dce580b4d2fb93c57616a373f46-associate-federal-external-affairs-us-climate-alliance-united-nations-foundation-washington</t>
+  </si>
+  <si>
+    <t>Building Porter- E. 162nd</t>
+  </si>
+  <si>
+    <t>Geel Community Services, Inc.</t>
+  </si>
+  <si>
+    <t>The Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 18.00/hour</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Disability, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20cf897592034ad481829522c27ca25f-building-porter-e-162nd-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Case Manager - Bedford</t>
+  </si>
+  <si>
+    <t>USD 56774.00 - 56774.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbd520c9faa34be397086d6995c18102-case-manager-bedford-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Case Manager (Grand Ave Studios)</t>
+  </si>
+  <si>
+    <t>USD 63052.17 - 63052.17/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d392e6ebbb34d24afe398ce051b4373-case-manager-grand-ave-studios-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Case Manager (Webster)</t>
+  </si>
+  <si>
+    <t>USD 57914.57 - 57914.57/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe39970f29834b63ac991f91c0a48c3a-case-manager-webster-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Clinical Coordinator- E. 162nd</t>
+  </si>
+  <si>
+    <t>USD 83886.03 - 83886.03/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c239652c3ef24f079934b454d887cbe9-clinical-coordinator-e-162nd-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Clinical Coordinator- Webster</t>
+  </si>
+  <si>
+    <t>USD 81443.18 - 81443.18/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e405a2c562e84d219adf5c630ea980e0-clinical-coordinator-webster-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>College Access Specialist</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of New York City</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8ba0406ed65541a886a29304126da91f-college-access-specialist-big-brothers-big-sisters-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>College and Career Success, Program Manager (Years 3 &amp; 4)</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7911b03d3deb404086b51f61de80f64c-college-and-career-success-program-manager-years-3-4-big-brothers-big-sisters-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Community Advocacy Manager</t>
+  </si>
+  <si>
+    <t>Groundwork RVA</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffd913c8a74e408faa8d2cc3931f4cfe-community-advocacy-manager-groundwork-rva-richmond</t>
+  </si>
+  <si>
+    <t>Community Wildfire Protection Plan Project Manager 1</t>
+  </si>
+  <si>
+    <t>The Ember Alliance</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3cfce4037374e3aa2e2ade2a11cdbde-community-wildfire-protection-plan-project-manager-1-the-ember-alliance-fort-collins</t>
+  </si>
+  <si>
+    <t>Content Specialist</t>
+  </si>
+  <si>
+    <t>BWF Zuri</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/79cbaacbdf3d4b70a06e122396384b30-content-specialist-bwf-zuri-bend</t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>COMMUNITY SERVINGS INC</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 19.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Health Medicine, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a075da2b298d4fff98b15f8f351ee86a-cook-community-servings-inc-boston</t>
+  </si>
+  <si>
+    <t>Corporate and Special Events Specialist</t>
+  </si>
+  <si>
+    <t>Broadway Cares/Equity Fights AIDS</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af6408d0511f428a9c121f96dce9cdfc-corporate-and-special-events-specialist-broadway-caresequity-fights-aids-new-york</t>
+  </si>
+  <si>
+    <t>Data Analyst</t>
+  </si>
+  <si>
+    <t>Coalition for the Homeless</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae4c48d3dd3d413b9f1c438822b8d661-data-analyst-coalition-for-the-homeless-new-york</t>
+  </si>
+  <si>
+    <t>Database Specialist</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f184cc0e3b4471a94e43bd208b077fa-database-specialist-big-brothers-big-sisters-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Deputy General Counsel</t>
+  </si>
+  <si>
+    <t>Mass. Executive Office of Housing and Livable Communities</t>
+  </si>
+  <si>
+    <t>USD 102855.80 - 158640.55/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/705cbb1ff3d3429b88014ea64d70fb0b-deputy-general-counsel-mass-executive-office-of-housing-and-livable-communities-boston</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4396d08ec2a948c8b67a219aee551b8d-development-associate-groundwork-rva-richmond</t>
+  </si>
+  <si>
+    <t>Development Officer, Special Events</t>
+  </si>
+  <si>
+    <t>SEEDS - Access Changes Everything</t>
+  </si>
+  <si>
+    <t>Newark, NJ</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/119fc470350444719c60ed7416b06e1e-development-officer-special-events-seeds-access-changes-everything-newark</t>
+  </si>
+  <si>
+    <t>Digital Organizer</t>
+  </si>
+  <si>
+    <t>Make the Road PA &amp; Make the Road Action PA</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 59000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/84807225cc184f90974b6470c1609122-digital-organizer-make-the-road-pa-make-the-road-action-pa-philadelphia</t>
+  </si>
+  <si>
+    <t>Director of Finance &amp; Administration</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e28549ae0854b36b401ca9f16d629e5-director-of-finance-administration-big-brothers-big-sisters-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Director of Major Giving</t>
+  </si>
+  <si>
+    <t>Cleveland Animal Protective League</t>
+  </si>
+  <si>
+    <t>Cleveland, Ohio</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd1acfe68a254148ac69694c7fcfce3f-director-of-major-giving-cleveland-animal-protective-league-cleveland</t>
+  </si>
+  <si>
+    <t>Director of Programs and Community Engagement</t>
+  </si>
+  <si>
+    <t>Alliance for Downtown New York, Inc.</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dabbe46997504a0e96e302cb7202a84b-director-of-programs-and-community-engagement-alliance-for-downtown-new-york-inc-new-york</t>
+  </si>
+  <si>
+    <t>Director, National Estate and Planned Giving</t>
+  </si>
+  <si>
+    <t>Anti-Defamation League</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c700aff6b07744d3aa3f01fc2eb52361-director-national-estate-and-planned-giving-anti-defamation-league-new-york</t>
+  </si>
+  <si>
+    <t>Director, Office of Justice, Peace, and Integrity of Creation (JPIC)</t>
+  </si>
+  <si>
+    <t>School Sisters of Notre Dame Atlantic-Midwest Province</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Environment, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/619a346ed7284985b2bdff99b3b7c2be-director-office-of-justice-peace-and-integrity-of-creation-jpic-school-sisters-of-notre-dame-atlantic-midwest-province-baltimore</t>
+  </si>
+  <si>
+    <t>Domestic Violence Resource Advocacy Coordinator</t>
+  </si>
+  <si>
+    <t>Women Aware, Inc.</t>
+  </si>
+  <si>
+    <t>New Brunswick, New Jersey</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fbb9ef47b97e4656a7ac9c621fe8ec16-domestic-violence-resource-advocacy-coordinator-women-aware-inc-new-brunswick</t>
+  </si>
+  <si>
+    <t>Educador(a) Social Júnior</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a05234229bfb43eca20265c8bf0873a4-educadora-social-junior-plan-international-brasil-codo</t>
+  </si>
+  <si>
+    <t>Employment and Education Specialist</t>
+  </si>
+  <si>
+    <t>AsylumWorks</t>
+  </si>
+  <si>
+    <t>Community Development, Immigrants Or Refugees, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4cf7033a843424e9995926372ae9d6c-employment-and-education-specialist-asylumworks-washington</t>
+  </si>
+  <si>
+    <t>EmpowHer Academy Instructor – Part-Time</t>
+  </si>
+  <si>
+    <t>EmpowHer Institute, Inc</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 27.50 - 27.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1f35ae22e1484d139a09aca2f1b0f20b-empowher-academy-instructor-part-time-empowher-institute-inc-los-angeles</t>
+  </si>
+  <si>
+    <t>The Concord Bridge</t>
+  </si>
+  <si>
+    <t>Concord, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Communications Access, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cce1ba399af244f399a75bfdfc412a78-executive-director-the-concord-bridge-concord</t>
+  </si>
+  <si>
+    <t>Chapel Hill Carrboro Public School Foundation</t>
+  </si>
+  <si>
+    <t>Chapel Hill, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/895eefac358140078cfa3290c4a47b87-executive-director-chapel-hill-carrboro-public-school-foundation-chapel-hill</t>
+  </si>
+  <si>
+    <t>Executive Director, Billerica Housing Authority</t>
+  </si>
+  <si>
+    <t>Massachusetts NAHRO</t>
+  </si>
+  <si>
+    <t>Billerica, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 101473.00 - 112748.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/467cf8d1bc474985a4538cacad4d1376-executive-director-billerica-housing-authority-massachusetts-nahro-billerica</t>
+  </si>
+  <si>
+    <t>Executive Director, Breakthrough Denver</t>
+  </si>
+  <si>
+    <t>Breakthrough Denver</t>
+  </si>
+  <si>
+    <t>Englewood, Colorado</t>
+  </si>
+  <si>
+    <t>USD 97000.00 - 127000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20ccff4de5964c70bc1a38a780ee281c-executive-director-breakthrough-denver-breakthrough-denver-englewood</t>
+  </si>
+  <si>
+    <t>Facilities Manager (Part time)</t>
+  </si>
+  <si>
+    <t>Unitarian Universalist Church of Silver Spring</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/277fb48766aa42d5aff95970e9a4924d-facilities-manager-part-time-unitarian-universalist-church-of-silver-spring-silver-spring</t>
+  </si>
+  <si>
+    <t>Faculty Member in Chemisty</t>
+  </si>
+  <si>
+    <t>College of the Atlantic (COA)</t>
+  </si>
+  <si>
+    <t>Bar Harbor, Maine</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/595bdde40f6448cd9a76c57769580fff-faculty-member-in-chemisty-college-of-the-atlantic-coa-bar-harbor</t>
+  </si>
+  <si>
+    <t>Gerente de Patrocínio/Sponsorship Manager</t>
+  </si>
+  <si>
+    <t>São Luís, Maranhão, BR</t>
+  </si>
+  <si>
+    <t>BRL 10173.00 - 10173.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e0755e5ee5349cca945c48d7bf629d5-gerente-de-patrociniosponsorship-manager-plan-international-brasil-sao-luis</t>
+  </si>
+  <si>
+    <t>Grant Writer</t>
+  </si>
+  <si>
+    <t>Young People's Chorus of NYC</t>
+  </si>
+  <si>
+    <t>USD 45.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d07fa6d826ae406c941c0c5c16cbea6c-grant-writer-young-peoples-chorus-of-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Human Resources &amp; Operations Manager</t>
+  </si>
+  <si>
+    <t>Joint Center for Political and Economic Studies</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Economic Development, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d032b1d738814182b338497a3259b09e-human-resources-operations-manager-joint-center-for-political-and-economic-studies-washington</t>
+  </si>
+  <si>
+    <t>Legal Aid Staff Attorney - Worcester</t>
+  </si>
+  <si>
+    <t>Community Legal Aid &amp; Affiliate</t>
+  </si>
+  <si>
+    <t>Worcester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 109000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5fad02d02f3433dbea0bf477f293bea-legal-aid-staff-attorney-worcester-community-legal-aid-affiliate-worcester</t>
+  </si>
+  <si>
+    <t>Legal Aid Staff Attorney (Western Mass)</t>
+  </si>
+  <si>
+    <t>Springfield, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/33ccfa0f793b471196b32ce7bc0b1012-legal-aid-staff-attorney-western-mass-community-legal-aid-affiliate-springfield</t>
+  </si>
+  <si>
+    <t>Literacy coach: Special Education &amp; Reading Intervention</t>
+  </si>
+  <si>
+    <t>Literacy How</t>
+  </si>
+  <si>
+    <t>North Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 75.00 - 100.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/60a4544086b64401bf528f57d891ce08-literacy-coach-special-education-reading-intervention-literacy-how-north-haven</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>United Community</t>
+  </si>
+  <si>
+    <t>Alexandria, Virginia</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/996574ca52fc4cb9a3db070b54d80141-major-gifts-officer-united-community-alexandria</t>
+  </si>
+  <si>
+    <t>Manager, Network Operations</t>
+  </si>
+  <si>
+    <t>SeriousFun Children's Network</t>
+  </si>
+  <si>
+    <t>Norwalk, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ce3059c497d4ea9b97e82ad71e7fb70-manager-network-operations-seriousfun-childrens-network-norwalk</t>
+  </si>
+  <si>
+    <t>Member Services Associate</t>
+  </si>
+  <si>
+    <t>New York - New Jersey Trail Conference</t>
+  </si>
+  <si>
+    <t>Mahwah, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Sports Recreation, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc749a5ea3134e87986651a74b08c965-member-services-associate-new-york-new-jersey-trail-conference-mahwah</t>
+  </si>
+  <si>
+    <t>Motorista</t>
+  </si>
+  <si>
+    <t>Salvador, Bahia, BR</t>
+  </si>
+  <si>
+    <t>BRL 2016.00 - 2016.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fde9515e357447483965a04e585ca49-motorista-plan-international-brasil-salvador</t>
+  </si>
+  <si>
+    <t>BRL 2106.00 - 2106.00/month</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3a6d2d3cb0d41ce8a6b1ca6c32a21cd-motorista-plan-international-brasil-codo</t>
+  </si>
+  <si>
+    <t>Officer, State Policy, Safer Chemicals Project</t>
+  </si>
+  <si>
+    <t>Pew Charitable Trusts</t>
+  </si>
+  <si>
+    <t>USD 121100.00 - 135400.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4bec3be515a64736aec4f7fafbcb573c-officer-state-policy-safer-chemicals-project-pew-charitable-trusts-washington</t>
+  </si>
+  <si>
+    <t>On Purpose Associate - A leadership programme for social &amp; environmental impact</t>
+  </si>
+  <si>
+    <t>On Purpose</t>
+  </si>
+  <si>
+    <t>London, England, GB</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>GBP 27010.00 - 27010.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1a5d856bb4144a8fac82f85feefbe7db-on-purpose-associate-a-leadership-programme-for-social-environmental-impact-on-purpose-london</t>
+  </si>
+  <si>
+    <t>Operations and Administration Manager</t>
+  </si>
+  <si>
+    <t>Torture Abolition and Survivor Support Coalition International (TASSC)</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/121ec7d252cf4d2b8ebc9860f7fd535d-operations-and-administration-manager-torture-abolition-and-survivor-support-coalition-international-tassc-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Youth Justice Network</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0742149098f34647abd3ea9cd67a1a96-program-coordinator-youth-justice-network-new-york</t>
+  </si>
+  <si>
+    <t>Program Manager, Community Based Mentoring</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c37d6ef17db44e49f40a75bcdf9242d-program-manager-community-based-mentoring-big-brothers-big-sisters-of-new-york-city-new-york</t>
+  </si>
+  <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>FirstPic, Inc.</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1b9440c433534456922be1cebf129cef-project-coordinator-firstpic-inc-annapolis</t>
+  </si>
+  <si>
+    <t>Project Director, Pro Truth Initiative</t>
+  </si>
+  <si>
+    <t>NAACP Legal Defense and Educational Fund, Inc.</t>
+  </si>
+  <si>
+    <t>USD 177000.00 - 204000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a46da0c69d1c43449a3b92b0acf4aa98-project-director-pro-truth-initiative-naacp-legal-defense-and-educational-fund-inc-washington</t>
+  </si>
+  <si>
+    <t>USD 184000.00 - 212000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8918b3b90c4a43ad87358dd4efee5e3a-project-director-pro-truth-initiative-naacp-legal-defense-and-educational-fund-inc-new-york</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 162500.00 - 186500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f3977c102784d43a17110efa1302724-project-director-pro-truth-initiative-naacp-legal-defense-and-educational-fund-inc-atlanta</t>
+  </si>
+  <si>
+    <t>REQUEST FOR APPLICATIONS (RFA): Tournament Management &amp; Fundraising Services — National Charity Soccer Tournament Series</t>
+  </si>
+  <si>
+    <t>Soccer Without Borders</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Sports Recreation, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6175f9b206854ea99685d4c486696ce2-request-for-applications-rfa-tournament-management-fundraising-services-national-charity-soccer-tournament-series-soccer-without-borders-baltimore</t>
+  </si>
+  <si>
+    <t>Senior Counsel (Employment &amp; Labor Focus)</t>
+  </si>
+  <si>
+    <t>Tides</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 132600.00 - 199000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Women, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fa35182ae9d4191acb757f63a05ca69-senior-counsel-employment-labor-focus-tides-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Director Immigrant Justice Legal Clinic</t>
+  </si>
+  <si>
+    <t>The Resurrection Project</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aaa8157d584d445a9bf35c6e7a94d27a-senior-director-immigrant-justice-legal-clinic-the-resurrection-project-chicago</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/305fccda569b49f5b02b6925df8e7166-sr-conservation-manager-conservation-campaigns-the-wilderness-society-washington</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>Wesley Theological Seminary</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Religion Spirituality, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61722d22b6884a7da5fae04a73808814-staff-accountant-wesley-theological-seminary-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Tenant Advocacy Program</t>
+  </si>
+  <si>
+    <t>Catholic Migration Services</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 79393.12 - 89846.66/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c5c4a508dc147d7bbbc841b17545fdb-staff-attorney-tenant-advocacy-program-catholic-migration-services-queens-county</t>
+  </si>
+  <si>
+    <t>Synagogue Receptionist / Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Central Synagogue</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f2c76f7eef854c0e87d81626b9ad4d05-synagogue-receptionist-administrative-assistant-central-synagogue-new-york</t>
+  </si>
+  <si>
+    <t>Teaching Positions in Palestine (Elementary School English)</t>
+  </si>
+  <si>
+    <t>Pioneers Baccalaureate School</t>
+  </si>
+  <si>
+    <t>Nablus, (no state), PS</t>
+  </si>
+  <si>
+    <t>ILS 2400.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b441b5b26b7a4fc8a2581ba0e506bbae-teaching-positions-in-palestine-elementary-school-english-pioneers-baccalaureate-school-nablus</t>
+  </si>
+  <si>
+    <t>Unit Director- ATP</t>
+  </si>
+  <si>
+    <t>USD 71904.97 - 71904.97/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3535c842baf4d9698f6bc30b9d21f51-unit-director-atp-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Video Editor</t>
+  </si>
+  <si>
+    <t>Block by Block Creative</t>
+  </si>
+  <si>
+    <t>Remote (CA)</t>
+  </si>
+  <si>
+    <t>CAD 38.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/5bd215fc2e4b483197d73fdda5f3820c-video-editor-block-by-block-creative-vancouver</t>
+  </si>
+  <si>
+    <t>Visiting Counselors- ATP</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7b3f6d5a205419284cf138edb162a17-visiting-counselors-atp-geel-community-services-inc-the-bronx</t>
+  </si>
+  <si>
+    <t>Visitor Services Associate</t>
+  </si>
+  <si>
+    <t>Fairfield Museum and History Center</t>
+  </si>
+  <si>
+    <t>Fairfield, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 17.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4cfdf94ebdaa4869b9170acb0536251c-visitor-services-associate-fairfield-museum-and-history-center-fairfield</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1650,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1676,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2058,706 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" t="s">
+        <v>117</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" t="s">
+        <v>136</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" t="s">
+        <v>150</v>
+      </c>
+      <c r="C29" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>152</v>
+      </c>
+      <c r="F29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" t="s">
+        <v>158</v>
+      </c>
+      <c r="F30" t="s">
+        <v>159</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +2765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +2804,64 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G2" t="s">
+        <v>167</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +2869,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +2908,1888 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" t="s">
+        <v>185</v>
+      </c>
+      <c r="F3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" t="s">
+        <v>192</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" t="s">
+        <v>204</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" t="s">
+        <v>201</v>
+      </c>
+      <c r="C7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>220</v>
+      </c>
+      <c r="B11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" t="s">
+        <v>223</v>
+      </c>
+      <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>226</v>
+      </c>
+      <c r="B12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" t="s">
+        <v>228</v>
+      </c>
+      <c r="F12" t="s">
+        <v>229</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E13" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" t="s">
+        <v>233</v>
+      </c>
+      <c r="G13" t="s">
+        <v>234</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" t="s">
+        <v>238</v>
+      </c>
+      <c r="D14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14" t="s">
+        <v>239</v>
+      </c>
+      <c r="F14" t="s">
+        <v>240</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>242</v>
+      </c>
+      <c r="B15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" t="s">
+        <v>165</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>245</v>
+      </c>
+      <c r="B16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" t="s">
+        <v>246</v>
+      </c>
+      <c r="F16" t="s">
+        <v>240</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>248</v>
+      </c>
+      <c r="B17" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D17" t="s">
+        <v>178</v>
+      </c>
+      <c r="E17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" t="s">
+        <v>240</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" t="s">
+        <v>252</v>
+      </c>
+      <c r="F18" t="s">
+        <v>240</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B19" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E19" t="s">
+        <v>255</v>
+      </c>
+      <c r="F19" t="s">
+        <v>240</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>257</v>
+      </c>
+      <c r="B20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C20" t="s">
+        <v>217</v>
+      </c>
+      <c r="D20" t="s">
+        <v>259</v>
+      </c>
+      <c r="E20" t="s">
+        <v>260</v>
+      </c>
+      <c r="F20" t="s">
+        <v>180</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>262</v>
+      </c>
+      <c r="B21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C21" t="s">
+        <v>217</v>
+      </c>
+      <c r="D21" t="s">
+        <v>178</v>
+      </c>
+      <c r="E21" t="s">
+        <v>263</v>
+      </c>
+      <c r="F21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>265</v>
+      </c>
+      <c r="B22" t="s">
+        <v>266</v>
+      </c>
+      <c r="C22" t="s">
+        <v>267</v>
+      </c>
+      <c r="D22" t="s">
+        <v>178</v>
+      </c>
+      <c r="E22" t="s">
+        <v>179</v>
+      </c>
+      <c r="F22" t="s">
+        <v>268</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>270</v>
+      </c>
+      <c r="B23" t="s">
+        <v>271</v>
+      </c>
+      <c r="C23" t="s">
+        <v>171</v>
+      </c>
+      <c r="D23" t="s">
+        <v>178</v>
+      </c>
+      <c r="E23" t="s">
+        <v>260</v>
+      </c>
+      <c r="F23" t="s">
+        <v>272</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>274</v>
+      </c>
+      <c r="B24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24" t="s">
+        <v>171</v>
+      </c>
+      <c r="D24" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24" t="s">
+        <v>179</v>
+      </c>
+      <c r="F24" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>278</v>
+      </c>
+      <c r="B25" t="s">
+        <v>279</v>
+      </c>
+      <c r="C25" t="s">
+        <v>280</v>
+      </c>
+      <c r="D25" t="s">
+        <v>178</v>
+      </c>
+      <c r="E25" t="s">
+        <v>281</v>
+      </c>
+      <c r="F25" t="s">
+        <v>282</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B26" t="s">
+        <v>285</v>
+      </c>
+      <c r="C26" t="s">
+        <v>217</v>
+      </c>
+      <c r="D26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" t="s">
+        <v>286</v>
+      </c>
+      <c r="F26" t="s">
+        <v>287</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>289</v>
+      </c>
+      <c r="B27" t="s">
+        <v>290</v>
+      </c>
+      <c r="C27" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" t="s">
+        <v>291</v>
+      </c>
+      <c r="F27" t="s">
+        <v>292</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>294</v>
+      </c>
+      <c r="B28" t="s">
+        <v>258</v>
+      </c>
+      <c r="C28" t="s">
+        <v>217</v>
+      </c>
+      <c r="D28" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" t="s">
+        <v>295</v>
+      </c>
+      <c r="F28" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>297</v>
+      </c>
+      <c r="B29" t="s">
+        <v>298</v>
+      </c>
+      <c r="C29" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" t="s">
+        <v>178</v>
+      </c>
+      <c r="E29" t="s">
+        <v>299</v>
+      </c>
+      <c r="F29" t="s">
+        <v>300</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>302</v>
+      </c>
+      <c r="B30" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E30" t="s">
+        <v>303</v>
+      </c>
+      <c r="F30" t="s">
+        <v>268</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>305</v>
+      </c>
+      <c r="B31" t="s">
+        <v>306</v>
+      </c>
+      <c r="C31" t="s">
+        <v>307</v>
+      </c>
+      <c r="D31" t="s">
+        <v>178</v>
+      </c>
+      <c r="E31" t="s">
+        <v>308</v>
+      </c>
+      <c r="F31" t="s">
+        <v>309</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>311</v>
+      </c>
+      <c r="B32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D32" t="s">
+        <v>178</v>
+      </c>
+      <c r="E32" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" t="s">
+        <v>315</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>317</v>
+      </c>
+      <c r="B33" t="s">
+        <v>258</v>
+      </c>
+      <c r="C33" t="s">
+        <v>217</v>
+      </c>
+      <c r="D33" t="s">
+        <v>178</v>
+      </c>
+      <c r="E33" t="s">
+        <v>318</v>
+      </c>
+      <c r="F33" t="s">
+        <v>180</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>320</v>
+      </c>
+      <c r="B34" t="s">
+        <v>321</v>
+      </c>
+      <c r="C34" t="s">
+        <v>322</v>
+      </c>
+      <c r="D34" t="s">
+        <v>178</v>
+      </c>
+      <c r="E34" t="s">
+        <v>323</v>
+      </c>
+      <c r="F34" t="s">
+        <v>324</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" t="s">
+        <v>327</v>
+      </c>
+      <c r="C35" t="s">
+        <v>208</v>
+      </c>
+      <c r="D35" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" t="s">
+        <v>328</v>
+      </c>
+      <c r="F35" t="s">
+        <v>329</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" t="s">
+        <v>332</v>
+      </c>
+      <c r="C36" t="s">
+        <v>217</v>
+      </c>
+      <c r="D36" t="s">
+        <v>178</v>
+      </c>
+      <c r="E36" t="s">
+        <v>333</v>
+      </c>
+      <c r="F36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>335</v>
+      </c>
+      <c r="B37" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" t="s">
+        <v>337</v>
+      </c>
+      <c r="D37" t="s">
+        <v>178</v>
+      </c>
+      <c r="E37" t="s">
+        <v>338</v>
+      </c>
+      <c r="F37" t="s">
+        <v>339</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>341</v>
+      </c>
+      <c r="B38" t="s">
+        <v>342</v>
+      </c>
+      <c r="C38" t="s">
+        <v>343</v>
+      </c>
+      <c r="D38" t="s">
+        <v>178</v>
+      </c>
+      <c r="E38" t="s">
+        <v>291</v>
+      </c>
+      <c r="F38" t="s">
+        <v>344</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>346</v>
+      </c>
+      <c r="B39" t="s">
+        <v>221</v>
+      </c>
+      <c r="C39" t="s">
+        <v>227</v>
+      </c>
+      <c r="D39" t="s">
+        <v>178</v>
+      </c>
+      <c r="E39" t="s">
+        <v>223</v>
+      </c>
+      <c r="F39" t="s">
+        <v>229</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>348</v>
+      </c>
+      <c r="B40" t="s">
+        <v>349</v>
+      </c>
+      <c r="C40" t="s">
+        <v>202</v>
+      </c>
+      <c r="D40" t="s">
+        <v>178</v>
+      </c>
+      <c r="E40" t="s">
+        <v>263</v>
+      </c>
+      <c r="F40" t="s">
+        <v>350</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>352</v>
+      </c>
+      <c r="B41" t="s">
+        <v>353</v>
+      </c>
+      <c r="C41" t="s">
+        <v>354</v>
+      </c>
+      <c r="D41" t="s">
+        <v>259</v>
+      </c>
+      <c r="E41" t="s">
+        <v>355</v>
+      </c>
+      <c r="F41" t="s">
+        <v>356</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" t="s">
+        <v>358</v>
+      </c>
+      <c r="C42" t="s">
+        <v>359</v>
+      </c>
+      <c r="D42" t="s">
+        <v>178</v>
+      </c>
+      <c r="E42" t="s">
+        <v>360</v>
+      </c>
+      <c r="F42" t="s">
+        <v>361</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+      <c r="B43" t="s">
+        <v>363</v>
+      </c>
+      <c r="C43" t="s">
+        <v>364</v>
+      </c>
+      <c r="D43" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" t="s">
+        <v>365</v>
+      </c>
+      <c r="F43" t="s">
+        <v>180</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>367</v>
+      </c>
+      <c r="B44" t="s">
+        <v>368</v>
+      </c>
+      <c r="C44" t="s">
+        <v>369</v>
+      </c>
+      <c r="D44" t="s">
+        <v>178</v>
+      </c>
+      <c r="E44" t="s">
+        <v>370</v>
+      </c>
+      <c r="F44" t="s">
+        <v>371</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>373</v>
+      </c>
+      <c r="B45" t="s">
+        <v>374</v>
+      </c>
+      <c r="C45" t="s">
+        <v>375</v>
+      </c>
+      <c r="D45" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" t="s">
+        <v>376</v>
+      </c>
+      <c r="F45" t="s">
+        <v>377</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>379</v>
+      </c>
+      <c r="B46" t="s">
+        <v>380</v>
+      </c>
+      <c r="C46" t="s">
+        <v>381</v>
+      </c>
+      <c r="D46" t="s">
+        <v>259</v>
+      </c>
+      <c r="E46" t="s">
+        <v>382</v>
+      </c>
+      <c r="F46" t="s">
+        <v>383</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>385</v>
+      </c>
+      <c r="B47" t="s">
+        <v>386</v>
+      </c>
+      <c r="C47" t="s">
+        <v>387</v>
+      </c>
+      <c r="D47" t="s">
+        <v>178</v>
+      </c>
+      <c r="E47" t="s">
+        <v>388</v>
+      </c>
+      <c r="F47" t="s">
+        <v>389</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>391</v>
+      </c>
+      <c r="B48" t="s">
+        <v>221</v>
+      </c>
+      <c r="C48" t="s">
+        <v>392</v>
+      </c>
+      <c r="D48" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" t="s">
+        <v>393</v>
+      </c>
+      <c r="F48" t="s">
+        <v>229</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>395</v>
+      </c>
+      <c r="B49" t="s">
+        <v>396</v>
+      </c>
+      <c r="C49" t="s">
+        <v>217</v>
+      </c>
+      <c r="D49" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" t="s">
+        <v>397</v>
+      </c>
+      <c r="F49" t="s">
+        <v>398</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>400</v>
+      </c>
+      <c r="B50" t="s">
+        <v>401</v>
+      </c>
+      <c r="C50" t="s">
+        <v>202</v>
+      </c>
+      <c r="D50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50" t="s">
+        <v>402</v>
+      </c>
+      <c r="F50" t="s">
+        <v>403</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>405</v>
+      </c>
+      <c r="B51" t="s">
+        <v>406</v>
+      </c>
+      <c r="C51" t="s">
+        <v>407</v>
+      </c>
+      <c r="D51" t="s">
+        <v>178</v>
+      </c>
+      <c r="E51" t="s">
+        <v>408</v>
+      </c>
+      <c r="F51" t="s">
+        <v>409</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>411</v>
+      </c>
+      <c r="B52" t="s">
+        <v>406</v>
+      </c>
+      <c r="C52" t="s">
+        <v>412</v>
+      </c>
+      <c r="D52" t="s">
+        <v>178</v>
+      </c>
+      <c r="E52" t="s">
+        <v>408</v>
+      </c>
+      <c r="F52" t="s">
+        <v>409</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>414</v>
+      </c>
+      <c r="B53" t="s">
+        <v>415</v>
+      </c>
+      <c r="C53" t="s">
+        <v>416</v>
+      </c>
+      <c r="D53" t="s">
+        <v>259</v>
+      </c>
+      <c r="E53" t="s">
+        <v>417</v>
+      </c>
+      <c r="F53" t="s">
+        <v>418</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>420</v>
+      </c>
+      <c r="B54" t="s">
+        <v>421</v>
+      </c>
+      <c r="C54" t="s">
+        <v>422</v>
+      </c>
+      <c r="D54" t="s">
+        <v>178</v>
+      </c>
+      <c r="E54" t="s">
+        <v>423</v>
+      </c>
+      <c r="F54" t="s">
+        <v>424</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>426</v>
+      </c>
+      <c r="B55" t="s">
+        <v>427</v>
+      </c>
+      <c r="C55" t="s">
+        <v>428</v>
+      </c>
+      <c r="D55" t="s">
+        <v>178</v>
+      </c>
+      <c r="E55" t="s">
+        <v>429</v>
+      </c>
+      <c r="F55" t="s">
+        <v>430</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>432</v>
+      </c>
+      <c r="B56" t="s">
+        <v>433</v>
+      </c>
+      <c r="C56" t="s">
+        <v>434</v>
+      </c>
+      <c r="D56" t="s">
+        <v>178</v>
+      </c>
+      <c r="E56" t="s">
+        <v>435</v>
+      </c>
+      <c r="F56" t="s">
+        <v>436</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>438</v>
+      </c>
+      <c r="B57" t="s">
+        <v>221</v>
+      </c>
+      <c r="C57" t="s">
+        <v>439</v>
+      </c>
+      <c r="D57" t="s">
+        <v>178</v>
+      </c>
+      <c r="E57" t="s">
+        <v>440</v>
+      </c>
+      <c r="F57" t="s">
+        <v>229</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>438</v>
+      </c>
+      <c r="B58" t="s">
+        <v>221</v>
+      </c>
+      <c r="C58" t="s">
+        <v>227</v>
+      </c>
+      <c r="D58" t="s">
+        <v>178</v>
+      </c>
+      <c r="E58" t="s">
+        <v>442</v>
+      </c>
+      <c r="F58" t="s">
+        <v>229</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>444</v>
+      </c>
+      <c r="B59" t="s">
+        <v>445</v>
+      </c>
+      <c r="C59" t="s">
+        <v>202</v>
+      </c>
+      <c r="D59" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59" t="s">
+        <v>446</v>
+      </c>
+      <c r="F59" t="s">
+        <v>165</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>448</v>
+      </c>
+      <c r="B60" t="s">
+        <v>449</v>
+      </c>
+      <c r="C60" t="s">
+        <v>450</v>
+      </c>
+      <c r="D60" t="s">
+        <v>451</v>
+      </c>
+      <c r="E60" t="s">
+        <v>452</v>
+      </c>
+      <c r="F60" t="s">
+        <v>453</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>455</v>
+      </c>
+      <c r="B61" t="s">
+        <v>456</v>
+      </c>
+      <c r="C61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D61" t="s">
+        <v>178</v>
+      </c>
+      <c r="E61" t="s">
+        <v>457</v>
+      </c>
+      <c r="F61" t="s">
+        <v>458</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>460</v>
+      </c>
+      <c r="B62" t="s">
+        <v>461</v>
+      </c>
+      <c r="C62" t="s">
+        <v>217</v>
+      </c>
+      <c r="D62" t="s">
+        <v>178</v>
+      </c>
+      <c r="E62" t="s">
+        <v>462</v>
+      </c>
+      <c r="F62" t="s">
+        <v>377</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>464</v>
+      </c>
+      <c r="B63" t="s">
+        <v>258</v>
+      </c>
+      <c r="C63" t="s">
+        <v>217</v>
+      </c>
+      <c r="D63" t="s">
+        <v>178</v>
+      </c>
+      <c r="E63" t="s">
+        <v>263</v>
+      </c>
+      <c r="F63" t="s">
+        <v>180</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>466</v>
+      </c>
+      <c r="B64" t="s">
+        <v>467</v>
+      </c>
+      <c r="C64" t="s">
+        <v>468</v>
+      </c>
+      <c r="D64" t="s">
+        <v>178</v>
+      </c>
+      <c r="E64" t="s">
+        <v>469</v>
+      </c>
+      <c r="F64" t="s">
+        <v>470</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>472</v>
+      </c>
+      <c r="B65" t="s">
+        <v>473</v>
+      </c>
+      <c r="C65" t="s">
+        <v>202</v>
+      </c>
+      <c r="D65" t="s">
+        <v>178</v>
+      </c>
+      <c r="E65" t="s">
+        <v>474</v>
+      </c>
+      <c r="F65" t="s">
+        <v>475</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>472</v>
+      </c>
+      <c r="B66" t="s">
+        <v>473</v>
+      </c>
+      <c r="C66" t="s">
+        <v>217</v>
+      </c>
+      <c r="D66" t="s">
+        <v>178</v>
+      </c>
+      <c r="E66" t="s">
+        <v>477</v>
+      </c>
+      <c r="F66" t="s">
+        <v>475</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>472</v>
+      </c>
+      <c r="B67" t="s">
+        <v>473</v>
+      </c>
+      <c r="C67" t="s">
+        <v>479</v>
+      </c>
+      <c r="D67" t="s">
+        <v>178</v>
+      </c>
+      <c r="E67" t="s">
+        <v>480</v>
+      </c>
+      <c r="F67" t="s">
+        <v>475</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>482</v>
+      </c>
+      <c r="B68" t="s">
+        <v>483</v>
+      </c>
+      <c r="C68" t="s">
+        <v>171</v>
+      </c>
+      <c r="D68" t="s">
+        <v>451</v>
+      </c>
+      <c r="E68" t="s">
+        <v>484</v>
+      </c>
+      <c r="F68" t="s">
+        <v>485</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>487</v>
+      </c>
+      <c r="B69" t="s">
+        <v>488</v>
+      </c>
+      <c r="C69" t="s">
+        <v>489</v>
+      </c>
+      <c r="D69" t="s">
+        <v>178</v>
+      </c>
+      <c r="E69" t="s">
+        <v>490</v>
+      </c>
+      <c r="F69" t="s">
+        <v>491</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>493</v>
+      </c>
+      <c r="B70" t="s">
+        <v>494</v>
+      </c>
+      <c r="C70" t="s">
+        <v>495</v>
+      </c>
+      <c r="D70" t="s">
+        <v>178</v>
+      </c>
+      <c r="E70" t="s">
+        <v>496</v>
+      </c>
+      <c r="F70" t="s">
+        <v>497</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>169</v>
+      </c>
+      <c r="B71" t="s">
+        <v>170</v>
+      </c>
+      <c r="C71" t="s">
+        <v>171</v>
+      </c>
+      <c r="D71" t="s">
+        <v>178</v>
+      </c>
+      <c r="E71" t="s">
+        <v>499</v>
+      </c>
+      <c r="F71" t="s">
+        <v>500</v>
+      </c>
+      <c r="G71" t="s">
+        <v>234</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>502</v>
+      </c>
+      <c r="B72" t="s">
+        <v>503</v>
+      </c>
+      <c r="C72" t="s">
+        <v>231</v>
+      </c>
+      <c r="D72" t="s">
+        <v>178</v>
+      </c>
+      <c r="E72" t="s">
+        <v>504</v>
+      </c>
+      <c r="F72" t="s">
+        <v>505</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>507</v>
+      </c>
+      <c r="B73" t="s">
+        <v>508</v>
+      </c>
+      <c r="C73" t="s">
+        <v>509</v>
+      </c>
+      <c r="D73" t="s">
+        <v>178</v>
+      </c>
+      <c r="E73" t="s">
+        <v>510</v>
+      </c>
+      <c r="F73" t="s">
+        <v>511</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>513</v>
+      </c>
+      <c r="B74" t="s">
+        <v>514</v>
+      </c>
+      <c r="C74" t="s">
+        <v>208</v>
+      </c>
+      <c r="D74" t="s">
+        <v>178</v>
+      </c>
+      <c r="E74" t="s">
+        <v>515</v>
+      </c>
+      <c r="F74" t="s">
+        <v>383</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>517</v>
+      </c>
+      <c r="B75" t="s">
+        <v>518</v>
+      </c>
+      <c r="C75" t="s">
+        <v>519</v>
+      </c>
+      <c r="D75" t="s">
+        <v>178</v>
+      </c>
+      <c r="E75" t="s">
+        <v>520</v>
+      </c>
+      <c r="F75" t="s">
+        <v>521</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>523</v>
+      </c>
+      <c r="B76" t="s">
+        <v>237</v>
+      </c>
+      <c r="C76" t="s">
+        <v>238</v>
+      </c>
+      <c r="D76" t="s">
+        <v>178</v>
+      </c>
+      <c r="E76" t="s">
+        <v>524</v>
+      </c>
+      <c r="F76" t="s">
+        <v>240</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>526</v>
+      </c>
+      <c r="B77" t="s">
+        <v>527</v>
+      </c>
+      <c r="C77" t="s">
+        <v>528</v>
+      </c>
+      <c r="D77" t="s">
+        <v>184</v>
+      </c>
+      <c r="E77" t="s">
+        <v>529</v>
+      </c>
+      <c r="F77" t="s">
+        <v>530</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>532</v>
+      </c>
+      <c r="B78" t="s">
+        <v>237</v>
+      </c>
+      <c r="C78" t="s">
+        <v>238</v>
+      </c>
+      <c r="D78" t="s">
+        <v>178</v>
+      </c>
+      <c r="E78" t="s">
+        <v>197</v>
+      </c>
+      <c r="F78" t="s">
+        <v>240</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>534</v>
+      </c>
+      <c r="B79" t="s">
+        <v>535</v>
+      </c>
+      <c r="C79" t="s">
+        <v>536</v>
+      </c>
+      <c r="D79" t="s">
+        <v>178</v>
+      </c>
+      <c r="E79" t="s">
+        <v>537</v>
+      </c>
+      <c r="F79" t="s">
+        <v>538</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-18.xlsx
+++ b/docs/xlsx/jobs-2026-09-18.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1408" uniqueCount="873">
   <si>
     <t>Title</t>
   </si>
@@ -430,6 +430,15 @@
     <t>https://www.conservationjobboard.com/job-listing-senior-program-manager---tennessee-urban-programs-chattanooga-tennessee/1329402220</t>
   </si>
   <si>
+    <t>State Program Coordinator</t>
+  </si>
+  <si>
+    <t>Portland or Eugene, OR</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-program-coordinator-portland-or-eugene-oregon/2658481435</t>
+  </si>
+  <si>
     <t>STEM Career Pathway Support Specialist Individual Placement</t>
   </si>
   <si>
@@ -523,6 +532,24 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/associate-federal-external-affairs-u-s-climate-alliance/</t>
   </si>
   <si>
+    <t>Chapter Director</t>
+  </si>
+  <si>
+    <t>Sierra Club</t>
+  </si>
+  <si>
+    <t>Portland, Oregon, United States</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/chapter-director-7/</t>
+  </si>
+  <si>
     <t>Sr. Conservation Manager, Conservation Campaigns</t>
   </si>
   <si>
@@ -535,9 +562,6 @@
     <t>80,000 - 100,000</t>
   </si>
   <si>
-    <t>Conservation</t>
-  </si>
-  <si>
     <t>https://greenjobs.greenjobsearch.org/jobs/sr-conservation-manager-conservation-campaigns/</t>
   </si>
   <si>
@@ -577,6 +601,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/27fca777d5754387819f749424fe70d8-academic-support-specialist-replications-inc-bronx-county</t>
   </si>
   <si>
+    <t>Administrative and IT Assistant</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Minnesota</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 58240.00 - 62400.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/390426c727244f21b50c8dd9bfb3b8ed-administrative-and-it-assistant-american-civil-liberties-union-of-minnesota-minneapolis</t>
+  </si>
+  <si>
     <t>Administrative Assistant – Cary Institute of Ecosystem Studies</t>
   </si>
   <si>
@@ -616,6 +658,45 @@
     <t>https://www.idealist.org/en/nonprofit-job/68c0903a2fe941dc9c45b41faf7a97b2-administrative-operations-manager-lift-louisiana-a-project-of-tides-center-new-orleans</t>
   </si>
   <si>
+    <t>After-School Site Coordinator</t>
+  </si>
+  <si>
+    <t>Homework Central</t>
+  </si>
+  <si>
+    <t>San Mateo, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc08326a22d24b4c85d26a4dce93e8c8-after-school-site-coordinator-homework-central-san-mateo</t>
+  </si>
+  <si>
+    <t>Alaska Campaign Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Anchorage, Alaska</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b2c275b0efb4b2dbddc809d42164911-alaska-campaign-associate-environment-america-anchorage</t>
+  </si>
+  <si>
     <t>Analytics Engineer</t>
   </si>
   <si>
@@ -676,6 +757,21 @@
     <t>https://www.idealist.org/en/job/773a8d42492e41c5a3236aadad0484eb-assistant-associate-or-full-professor-tenure-track-or-tenure-architecture-and-urban-ai-cuny-school-of-professional-studies-new-york</t>
   </si>
   <si>
+    <t>Assistant: Extreme Risk Protection Order Unit (3913)</t>
+  </si>
+  <si>
+    <t>New York State Office of the Attorney General</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 87356.00 - 186493.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/3fab74296d474c4ba7b0b8f48bd0a79e-assistant-extreme-risk-protection-order-unit-3913-new-york-state-office-of-the-attorney-general-albany</t>
+  </si>
+  <si>
     <t>Assistente de Projetos Sociais Júnior</t>
   </si>
   <si>
@@ -742,6 +838,78 @@
     <t>https://www.idealist.org/en/nonprofit-job/20cf897592034ad481829522c27ca25f-building-porter-e-162nd-geel-community-services-inc-the-bronx</t>
   </si>
   <si>
+    <t>Campaign Organizer</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 40250.00 - 40250.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb8938729d3942bb8db51b26a8d36f4b-campaign-organizer-environment-america-denver</t>
+  </si>
+  <si>
+    <t>Canvass Office Director</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 53750.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3212924556e74f18a595c2c07e6c26ef-canvass-office-director-environment-america-chicago</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f59394bbc1db412a85e8f04ec3c97f5d-canvass-office-director-environment-america-seattle</t>
+  </si>
+  <si>
+    <t>Santa Cruz, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e2902073f3174aa2bd22057c8dde9d9b-canvass-office-director-environment-america-santa-cruz</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/be09ba1d1a4142728beecf943aeda199-canvass-office-director-environment-america-denver</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f0e2e89a874409793baa2a533f96bd7-canvass-office-director-environment-america-oakland</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8cf171c6af0e4cb28f54f01bac1af9c0-canvass-office-director-environment-america-boston</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6713fd61261b4b7d8d105ca269063b4c-canvass-office-director-environment-america-washington</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64a7bb265a4c45ada336c5a6f54a9b6a-canvass-office-director-environment-america-philadelphia</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a5704992f2d4fb8b57a86fa94bc74bb-canvass-office-director-environment-america-portland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b8a359350d34ea0adb40c797179506b-canvass-office-director-environment-america-minneapolis</t>
+  </si>
+  <si>
     <t>Case Manager - Bedford</t>
   </si>
   <si>
@@ -769,6 +937,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/fe39970f29834b63ac991f91c0a48c3a-case-manager-webster-geel-community-services-inc-the-bronx</t>
   </si>
   <si>
+    <t>Chief Development and Communications Officer</t>
+  </si>
+  <si>
+    <t>Seva Foundation</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d2babebeba64d8cae66ee0ac1000021-chief-development-and-communications-officer-seva-foundation-berkeley</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer</t>
+  </si>
+  <si>
+    <t>Randall's Island Park Alliance, Inc.</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 185000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84de4921c0fa4246bf975709bed500a3-chief-financial-officer-randalls-island-park-alliance-inc-new-york</t>
+  </si>
+  <si>
+    <t>Chief Staff Officer - SHARE Enterprise IT Community Association</t>
+  </si>
+  <si>
+    <t>Smithbucklin</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/402df42a0f7e4305ba808c3b0372831e-chief-staff-officer-share-enterprise-it-community-association-smithbucklin-chicago</t>
+  </si>
+  <si>
+    <t>Chief Staff Officer- International Association of Business Communicators (IABC)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/7de91b07e2b44bab924b9e71245b714e-chief-staff-officer-international-association-of-business-communicators-iabc-smithbucklin-chicago</t>
+  </si>
+  <si>
+    <t>Client Services Specialist</t>
+  </si>
+  <si>
+    <t>Jenesse Center</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Crime Safety, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/26b19255b9224fb8b56edb2e1728fe87-client-services-specialist-jenesse-center-los-angeles</t>
+  </si>
+  <si>
     <t>Clinical Coordinator- E. 162nd</t>
   </si>
   <si>
@@ -793,9 +1027,6 @@
     <t>Big Brothers Big Sisters of New York City</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 30.00 - 30.00/hour</t>
   </si>
   <si>
@@ -832,9 +1063,6 @@
     <t>The Ember Alliance</t>
   </si>
   <si>
-    <t>Civic Engagement, Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d3cfce4037374e3aa2e2ade2a11cdbde-community-wildfire-protection-plan-project-manager-1-the-ember-alliance-fort-collins</t>
   </si>
   <si>
@@ -856,9 +1084,6 @@
     <t>COMMUNITY SERVINGS INC</t>
   </si>
   <si>
-    <t>Boston, Massachusetts</t>
-  </si>
-  <si>
     <t>USD 19.00/hour</t>
   </si>
   <si>
@@ -868,6 +1093,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a075da2b298d4fff98b15f8f351ee86a-cook-community-servings-inc-boston</t>
   </si>
   <si>
+    <t>COORDINATING DIRECTOR - ARTS PROGRAM (Full-time)</t>
+  </si>
+  <si>
+    <t>ASE Global Bridges</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78490da9c8fa4fac8c2341fb6dcb82ef-coordinating-director-arts-program-full-time-ase-global-bridges-new-york</t>
+  </si>
+  <si>
     <t>Corporate and Special Events Specialist</t>
   </si>
   <si>
@@ -907,6 +1147,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/1f184cc0e3b4471a94e43bd208b077fa-database-specialist-big-brothers-big-sisters-of-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Deputy Director</t>
+  </si>
+  <si>
+    <t>Community Partners in Caring</t>
+  </si>
+  <si>
+    <t>Santa Maria, California</t>
+  </si>
+  <si>
+    <t>USD 74880.00 - 83200.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61d6f9ab006b4537979999c591ad006f-deputy-director-community-partners-in-caring-santa-maria</t>
+  </si>
+  <si>
     <t>Deputy General Counsel</t>
   </si>
   <si>
@@ -931,6 +1189,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/4396d08ec2a948c8b67a219aee551b8d-development-associate-groundwork-rva-richmond</t>
   </si>
   <si>
+    <t>Tri-State Transportation Campaign</t>
+  </si>
+  <si>
+    <t>USD 2800.00 - 3500.00/month</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6a9d7977ca948799b2b613c7a9fa466-development-associate-tri-state-transportation-campaign-new-york</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>SEAL (Sobrato Early Academic Language Program)</t>
+  </si>
+  <si>
+    <t>Milpitas, California</t>
+  </si>
+  <si>
+    <t>USD 183000.00 - 183000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdf568d5e73f4e6093e6979f316f8ac8-development-director-seal-sobrato-early-academic-language-program-milpitas</t>
+  </si>
+  <si>
     <t>Development Officer, Special Events</t>
   </si>
   <si>
@@ -949,15 +1237,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/119fc470350444719c60ed7416b06e1e-development-officer-special-events-seeds-access-changes-everything-newark</t>
   </si>
   <si>
+    <t>Digital Marketing Coordinator</t>
+  </si>
+  <si>
+    <t>iMission Institute</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/be515795abb441f582d33963a1d3f852-digital-marketing-coordinator-imission-institute-new-haven</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/7295d6acd67d418a8e6900292fe2fb4b-digital-marketing-coordinator-imission-institute-detroit</t>
+  </si>
+  <si>
     <t>Digital Organizer</t>
   </si>
   <si>
     <t>Make the Road PA &amp; Make the Road Action PA</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>USD 55000.00 - 59000.00/year</t>
   </si>
   <si>
@@ -967,6 +1276,51 @@
     <t>https://www.idealist.org/en/job/84807225cc184f90974b6470c1609122-digital-organizer-make-the-road-pa-make-the-road-action-pa-philadelphia</t>
   </si>
   <si>
+    <t>Direct Appeals Attorney at CAL</t>
+  </si>
+  <si>
+    <t>Center for Appellate Litigation</t>
+  </si>
+  <si>
+    <t>USD 94139.00 - 122655.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7c27ee4a06e74d419c14580794fde505-direct-appeals-attorney-at-cal-center-for-appellate-litigation-new-york</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Growing Up Green Charter School</t>
+  </si>
+  <si>
+    <t>Queens, New York</t>
+  </si>
+  <si>
+    <t>USD 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/849952b46f6343098beb8f0e41ba0626-director-of-development-growing-up-green-charter-school-queens</t>
+  </si>
+  <si>
+    <t>Her Justice</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Women, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ea6e3947756422f94448ffb7a2e1c3e-director-of-development-her-justice-new-york</t>
+  </si>
+  <si>
     <t>Director of Finance &amp; Administration</t>
   </si>
   <si>
@@ -976,6 +1330,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/0e28549ae0854b36b401ca9f16d629e5-director-of-finance-administration-big-brothers-big-sisters-of-new-york-city-new-york</t>
   </si>
   <si>
+    <t>Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>Centro de Trabajadores Unidos En Lucha (CTUL)</t>
+  </si>
+  <si>
+    <t>USD 87550.00 - 87550.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d9676f5b81464d26be26d01e02e4371f-director-of-finance-and-operations-centro-de-trabajadores-unidos-en-lucha-ctul-minneapolis</t>
+  </si>
+  <si>
     <t>Director of Major Giving</t>
   </si>
   <si>
@@ -1009,15 +1375,57 @@
     <t>https://www.idealist.org/en/nonprofit-job/dabbe46997504a0e96e302cb7202a84b-director-of-programs-and-community-engagement-alliance-for-downtown-new-york-inc-new-york</t>
   </si>
   <si>
+    <t>Director of State Programs</t>
+  </si>
+  <si>
+    <t>U.S. PIRG</t>
+  </si>
+  <si>
+    <t>USD 43500.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Transparency Oversight, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ff563ded4c6410b9522395a3a8d6faf-director-of-state-programs-us-pirg-philadelphia</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d58e0e084044c2bb07d6aef0317ab27-director-of-state-programs-us-pirg-baltimore</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1864064244904612aa309e4f85b7ae38-director-of-state-programs-us-pirg-madison</t>
+  </si>
+  <si>
+    <t>Director, Development</t>
+  </si>
+  <si>
+    <t>Youth Organize! California</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 118320.00 - 118320.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/763bddec17984822bd71f4c4faca3a9e-director-development-youth-organize-california-los-angeles</t>
+  </si>
+  <si>
     <t>Director, National Estate and Planned Giving</t>
   </si>
   <si>
     <t>Anti-Defamation League</t>
   </si>
   <si>
-    <t>USD 170000.00 - 180000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c700aff6b07744d3aa3f01fc2eb52361-director-national-estate-and-planned-giving-anti-defamation-league-new-york</t>
   </si>
   <si>
@@ -1027,9 +1435,6 @@
     <t>School Sisters of Notre Dame Atlantic-Midwest Province</t>
   </si>
   <si>
-    <t>Baltimore, Maryland</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 85000.00/year</t>
   </si>
   <si>
@@ -1039,6 +1444,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/619a346ed7284985b2bdff99b3b7c2be-director-office-of-justice-peace-and-integrity-of-creation-jpic-school-sisters-of-notre-dame-atlantic-midwest-province-baltimore</t>
   </si>
   <si>
+    <t>Docente de regularización y nivelación educativa en Saltillo ( Presencial)</t>
+  </si>
+  <si>
+    <t>Educación para Compartir - México</t>
+  </si>
+  <si>
+    <t>Saltillo, Coahuila de Zaragoza, MX</t>
+  </si>
+  <si>
+    <t>MXN 15000.00 - 15000.00/month</t>
+  </si>
+  <si>
+    <t>Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4134b5d765d411e922511c9c5612b16-docente-de-regularizacion-y-nivelacion-educativa-en-saltillo-presencial-educacion-para-compartir-mexico-saltillo</t>
+  </si>
+  <si>
     <t>Domestic Violence Resource Advocacy Coordinator</t>
   </si>
   <si>
@@ -1060,6 +1483,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/a05234229bfb43eca20265c8bf0873a4-educadora-social-junior-plan-international-brasil-codo</t>
   </si>
   <si>
+    <t>Elder Law Practice Group Chair</t>
+  </si>
+  <si>
+    <t>Legal Services of Northern Virginia</t>
+  </si>
+  <si>
+    <t>Fairfax, Virginia</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6abfad3a76bc412485003a3ed002a31f-elder-law-practice-group-chair-legal-services-of-northern-virginia-fairfax</t>
+  </si>
+  <si>
     <t>Employment and Education Specialist</t>
   </si>
   <si>
@@ -1078,9 +1519,6 @@
     <t>EmpowHer Institute, Inc</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 27.50 - 27.50/hour</t>
   </si>
   <si>
@@ -1090,6 +1528,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/1f35ae22e1484d139a09aca2f1b0f20b-empowher-academy-instructor-part-time-empowher-institute-inc-los-angeles</t>
   </si>
   <si>
+    <t>End Food Waste Campaign Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7deb1d042d784f30a840099583760fa9-end-food-waste-campaign-associate-environment-america-portland</t>
+  </si>
+  <si>
+    <t>Enrollment &amp; Match Specialist</t>
+  </si>
+  <si>
+    <t>Big Brothers Big Sisters of the Bay Area (BBBSBA)</t>
+  </si>
+  <si>
+    <t>USD 27.88 - 30.28/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/45ae074692aa4c4bb5c3ec8f8e63c71c-enrollment-match-specialist-big-brothers-big-sisters-of-the-bay-area-bbbsba-oakland</t>
+  </si>
+  <si>
+    <t>Executive Assistant, Office of the President</t>
+  </si>
+  <si>
+    <t>United Way of King County (WA State)</t>
+  </si>
+  <si>
+    <t>USD 36.54 - 38.46/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f055b206c8c448c48cb57bfd1cf6bd69-executive-assistant-office-of-the-president-united-way-of-king-county-wa-state-seattle</t>
+  </si>
+  <si>
     <t>The Concord Bridge</t>
   </si>
   <si>
@@ -1117,6 +1588,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/895eefac358140078cfa3290c4a47b87-executive-director-chapel-hill-carrboro-public-school-foundation-chapel-hill</t>
   </si>
   <si>
+    <t>FRIENDS OF ROGERS ENVIRONMENTAL ED CENTER INC</t>
+  </si>
+  <si>
+    <t>Sherburne, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe748ad8c37c43f38303f77920035b26-executive-director-friends-of-rogers-environmental-ed-center-inc-sherburne</t>
+  </si>
+  <si>
+    <t>Executive Director - Bank Insurance &amp; Securities Association</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 225000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/35b82dd0027446a0abc426f45b0e0000-executive-director-bank-insurance-securities-association-smithbucklin-washington</t>
+  </si>
+  <si>
     <t>Executive Director, Billerica Housing Authority</t>
   </si>
   <si>
@@ -1189,6 +1684,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/595bdde40f6448cd9a76c57769580fff-faculty-member-in-chemisty-college-of-the-atlantic-coa-bar-harbor</t>
   </si>
   <si>
+    <t>Federal Campaigns Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86a597f9899b430db22f45f77061b9b6-federal-campaigns-associate-environment-america-washington</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>Big Bear Retreat Center</t>
+  </si>
+  <si>
+    <t>Big Bear, California</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/4e0a4789c56a430c96139da477e5d29b-general-manager-big-bear-retreat-center-big-bear</t>
+  </si>
+  <si>
     <t>Gerente de Patrocínio/Sponsorship Manager</t>
   </si>
   <si>
@@ -1216,6 +1732,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/d07fa6d826ae406c941c0c5c16cbea6c-grant-writer-young-peoples-chorus-of-nyc-new-york</t>
   </si>
   <si>
+    <t>Housing Attorney</t>
+  </si>
+  <si>
+    <t>Legal Aid Society of San Mateo County</t>
+  </si>
+  <si>
+    <t>Redwood City, California</t>
+  </si>
+  <si>
+    <t>USD 86000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Health Medicine, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f970ae06cd248418a0cd54fc2cb5286-housing-attorney-legal-aid-society-of-san-mateo-county-redwood-city</t>
+  </si>
+  <si>
     <t>Human Resources &amp; Operations Manager</t>
   </si>
   <si>
@@ -1231,6 +1765,87 @@
     <t>https://www.idealist.org/en/nonprofit-job/d032b1d738814182b338497a3259b09e-human-resources-operations-manager-joint-center-for-political-and-economic-studies-washington</t>
   </si>
   <si>
+    <t>Human Resources Generalist</t>
+  </si>
+  <si>
+    <t>Heal the Bay</t>
+  </si>
+  <si>
+    <t>Santa Monica, California</t>
+  </si>
+  <si>
+    <t>USD 34.61 - 39.42/hour</t>
+  </si>
+  <si>
+    <t>Education, Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2a63d530c094dfa82bb13203b9829cd-human-resources-generalist-heal-the-bay-santa-monica</t>
+  </si>
+  <si>
+    <t>Immigration Paralegal</t>
+  </si>
+  <si>
+    <t>USD 66500.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Legal Assistance, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3409f16020e4453e98761971c08a85c5-immigration-paralegal-her-justice-new-york</t>
+  </si>
+  <si>
+    <t>Immigration Staff Attorney</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2fd58d43daf45d2aed0e0de4f8d896e-immigration-staff-attorney-her-justice-new-york</t>
+  </si>
+  <si>
+    <t>Joan Cirillo Emerging Journalist Fellow</t>
+  </si>
+  <si>
+    <t>OPB</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>USD 37.73 - 37.73/hour</t>
+  </si>
+  <si>
+    <t>Media, Philanthropy, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac7b77b228c04a819d62f815b0cd1bd0-joan-cirillo-emerging-journalist-fellow-opb-portland</t>
+  </si>
+  <si>
+    <t>Law Site Manager</t>
+  </si>
+  <si>
+    <t>Fresh Lifelines for Youth</t>
+  </si>
+  <si>
+    <t>Redwood City, CA</t>
+  </si>
+  <si>
+    <t>USD 29.69 - 29.69/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d26e9ad690db4cfd91638f7a136d5fc6-law-site-manager-fresh-lifelines-for-youth-redwood-city</t>
+  </si>
+  <si>
+    <t>Leadership and STAY FLY Programs Coordinator</t>
+  </si>
+  <si>
+    <t>USD 27.53 - 27.53/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/913ca4d3f5744d8584b7cce799e69da7-leadership-and-stay-fly-programs-coordinator-fresh-lifelines-for-youth-redwood-city</t>
+  </si>
+  <si>
     <t>Legal Aid Staff Attorney - Worcester</t>
   </si>
   <si>
@@ -1294,6 +1909,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/996574ca52fc4cb9a3db070b54d80141-major-gifts-officer-united-community-alexandria</t>
   </si>
   <si>
+    <t>Village Health Works</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d27883e9d752449e9a6b153e3df2ec17-major-gifts-officer-village-health-works-new-york</t>
+  </si>
+  <si>
+    <t>Manager of Marketing and Communications</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bb126da2ddf44fcb5ac27461e72bb05-manager-of-marketing-and-communications-big-brothers-big-sisters-of-the-bay-area-bbbsba-oakland</t>
+  </si>
+  <si>
     <t>Manager, Network Operations</t>
   </si>
   <si>
@@ -1312,6 +1948,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/4ce3059c497d4ea9b97e82ad71e7fb70-manager-network-operations-seriousfun-childrens-network-norwalk</t>
   </si>
   <si>
+    <t>Map Nurse</t>
+  </si>
+  <si>
+    <t>Victory Human Services</t>
+  </si>
+  <si>
+    <t>USD 38.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1573b473bb084b2ca81914a9fab10ab5-map-nurse-victory-human-services-boston</t>
+  </si>
+  <si>
+    <t>Marketing and Communications Manager</t>
+  </si>
+  <si>
+    <t>Team Survivor Northwest</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/463c2ed59a614f71bd536cfc7a446fcf-marketing-and-communications-manager-team-survivor-northwest-seattle</t>
+  </si>
+  <si>
     <t>Member Services Associate</t>
   </si>
   <si>
@@ -1348,6 +2011,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/d3a6d2d3cb0d41ce8a6b1ca6c32a21cd-motorista-plan-international-brasil-codo</t>
   </si>
   <si>
+    <t>News Assistant</t>
+  </si>
+  <si>
+    <t>Simons Foundation</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b2ae2187cd134fb19f893139f48f320d-news-assistant-simons-foundation-new-york</t>
+  </si>
+  <si>
     <t>Officer, State Policy, Safer Chemicals Project</t>
   </si>
   <si>
@@ -1369,9 +2044,6 @@
     <t>London, England, GB</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>GBP 27010.00 - 27010.00/year</t>
   </si>
   <si>
@@ -1396,18 +2068,111 @@
     <t>https://www.idealist.org/en/nonprofit-job/121ec7d252cf4d2b8ebc9860f7fd535d-operations-and-administration-manager-torture-abolition-and-survivor-support-coalition-international-tassc-washington</t>
   </si>
   <si>
+    <t>Organizing Fellow for 2026 Elections</t>
+  </si>
+  <si>
+    <t>Student PIRGs</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 44450.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dea39eedb3844f7a9c772048f4671e91-organizing-fellow-for-2026-elections-student-pirgs-philadelphia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c38ae785fee444519e4d3886baf7b2cd-organizing-fellow-for-2026-elections-student-pirgs-madison</t>
+  </si>
+  <si>
+    <t>Tampa, Florida</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e1c1bcff08840ac854bb00be0b0886b-organizing-fellow-for-2026-elections-student-pirgs-tampa</t>
+  </si>
+  <si>
+    <t>Part-Time Temporary Knowledge Management Officer | 4 months+ | Public Health Non-Profit | Hybrid NYC</t>
+  </si>
+  <si>
+    <t>TSS - Temporary Staffing + Search</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 39.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6288601c6c38447795eff0456015bcdf-part-time-temporary-knowledge-management-officer-4-months-public-health-non-profit-hybrid-nyc-tss-temporary-staffing-search-new-york</t>
+  </si>
+  <si>
+    <t>PennEnvironment Clean Water and Conservation Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d1385500354943f3adb3dd4437baed81-pennenvironment-clean-water-and-conservation-associate-environment-america-philadelphia</t>
+  </si>
+  <si>
+    <t>Professional Education Coordinator</t>
+  </si>
+  <si>
+    <t>DORIS DUKE MANAGEMENT FOUNDATION</t>
+  </si>
+  <si>
+    <t>Hillsborough, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2094808dfd504e619baeda99c4d0c21b-professional-education-coordinator-doris-duke-management-foundation-hillsborough</t>
+  </si>
+  <si>
+    <t>Program and Development Coordinator – Midwest</t>
+  </si>
+  <si>
+    <t>Shalom Hartman Institute of North America</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2197cfbca84145f3a0fdf7bc6945b6e5-program-and-development-coordinator-midwest-shalom-hartman-institute-of-north-america-detroit</t>
+  </si>
+  <si>
+    <t>Program Associate, Mellon Mays Programs</t>
+  </si>
+  <si>
+    <t>American Council of Learned Societies</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0aaf285672024f26be18e79a8d2a2c09-program-associate-mellon-mays-programs-american-council-of-learned-societies-new-york</t>
+  </si>
+  <si>
     <t>Program Coordinator</t>
   </si>
   <si>
     <t>Youth Justice Network</t>
   </si>
   <si>
-    <t>USD 55000.00 - 60000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/0742149098f34647abd3ea9cd67a1a96-program-coordinator-youth-justice-network-new-york</t>
   </si>
   <si>
+    <t>Connecticut Outdoor &amp; Environmental Education Association</t>
+  </si>
+  <si>
+    <t>West Hartford, Connecticut</t>
+  </si>
+  <si>
+    <t>Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c2edd3e93a564056bbedc3c762efbf5a-program-coordinator-connecticut-outdoor-environmental-education-association-west-hartford</t>
+  </si>
+  <si>
     <t>Program Manager, Community Based Mentoring</t>
   </si>
   <si>
@@ -1462,6 +2227,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/2f3977c102784d43a17110efa1302724-project-director-pro-truth-initiative-naacp-legal-defense-and-educational-fund-inc-atlanta</t>
   </si>
   <si>
+    <t>Psychiatric Nurse Practitioner</t>
+  </si>
+  <si>
+    <t>N Street Village, Inc.</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a8ead3394caf418c97e85787ed67f710-psychiatric-nurse-practitioner-n-street-village-inc-washington</t>
+  </si>
+  <si>
+    <t>Regional Director, Western States</t>
+  </si>
+  <si>
+    <t>Movement Voter Project</t>
+  </si>
+  <si>
+    <t>USD 142800.00 - 163200.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74a99720b317487c99fb864f4bb1706b-regional-director-western-states-movement-voter-project-northampton</t>
+  </si>
+  <si>
     <t>REQUEST FOR APPLICATIONS (RFA): Tournament Management &amp; Fundraising Services — National Charity Soccer Tournament Series</t>
   </si>
   <si>
@@ -1477,15 +2272,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/6175f9b206854ea99685d4c486696ce2-request-for-applications-rfa-tournament-management-fundraising-services-national-charity-soccer-tournament-series-soccer-without-borders-baltimore</t>
   </si>
   <si>
+    <t>School Program Specialist</t>
+  </si>
+  <si>
+    <t>USD 28.84 - 30.77/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eb50c7ffa4ab4e769771c0989c26fc29-school-program-specialist-big-brothers-big-sisters-of-the-bay-area-bbbsba-oakland</t>
+  </si>
+  <si>
     <t>Senior Counsel (Employment &amp; Labor Focus)</t>
   </si>
   <si>
     <t>Tides</t>
   </si>
   <si>
-    <t>Remote (California)</t>
-  </si>
-  <si>
     <t>USD 132600.00 - 199000.00/year</t>
   </si>
   <si>
@@ -1495,33 +2296,177 @@
     <t>https://www.idealist.org/en/nonprofit-job/8fa35182ae9d4191acb757f63a05ca69-senior-counsel-employment-labor-focus-tides-san-francisco</t>
   </si>
   <si>
+    <t>SENIOR DEVELOPMENT ASSOCIATE – Events &amp; Individual Giving POSITION DESCRIPTION</t>
+  </si>
+  <si>
+    <t>Access Living of Metropolitan Chicago</t>
+  </si>
+  <si>
+    <t>Disability, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cacc0b1af7574c6b9c710d8dc99a59ae-senior-development-associate-events-individual-giving-position-description-access-living-of-metropolitan-chicago-chicago</t>
+  </si>
+  <si>
     <t>Senior Director Immigrant Justice Legal Clinic</t>
   </si>
   <si>
     <t>The Resurrection Project</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 120000.00 - 135000.00/year</t>
   </si>
   <si>
-    <t>Community Development, Economic Development, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/aaa8157d584d445a9bf35c6e7a94d27a-senior-director-immigrant-justice-legal-clinic-the-resurrection-project-chicago</t>
   </si>
   <si>
+    <t>Senior Director of Finance and Operations</t>
+  </si>
+  <si>
+    <t>Eva's Village - Saving and Changing Lives Since 1982</t>
+  </si>
+  <si>
+    <t>Paterson, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/866cd90aee394c189dbaea53cc605355-senior-director-of-finance-and-operations-evas-village-saving-and-changing-lives-since-1982-paterson</t>
+  </si>
+  <si>
+    <t>Senior Director, Media</t>
+  </si>
+  <si>
+    <t>BRIC</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e8eece660e64d98b7dc23d0063aa5ff-senior-director-media-bric-brooklyn</t>
+  </si>
+  <si>
+    <t>Senior Manager of Operations</t>
+  </si>
+  <si>
+    <t>Museum of Jewish Heritage - A Living Memorial to the Holocaust</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7930f03e57f04ba494fa288f0122b7a6-senior-manager-of-operations-museum-of-jewish-heritage-a-living-memorial-to-the-holocaust-new-york</t>
+  </si>
+  <si>
+    <t>Senior Social Worker - Mobile Crisis Response Team (MCRT)</t>
+  </si>
+  <si>
+    <t>People USA</t>
+  </si>
+  <si>
+    <t>New Rochelle, New York</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/416cc83a60df4953913bc4b3eb34b676-senior-social-worker-mobile-crisis-response-team-mcrt-people-usa-new-rochelle</t>
+  </si>
+  <si>
+    <t>Senior Source Water Policy Manager</t>
+  </si>
+  <si>
+    <t>Alliance for the Great Lakes</t>
+  </si>
+  <si>
+    <t>Remote (Ohio)</t>
+  </si>
+  <si>
+    <t>USD 90000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/577aa668508f4918a25bb2a3bb6169a1-senior-source-water-policy-manager-alliance-for-the-great-lakes-chicago</t>
+  </si>
+  <si>
+    <t>Senior Specialist, Major Gifts</t>
+  </si>
+  <si>
+    <t>National Immigration Law Center</t>
+  </si>
+  <si>
+    <t>USD 89300.00 - 111600.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cdc04f3c425c4a7b8aec940d1bcb15de-senior-specialist-major-gifts-national-immigration-law-center-new-york</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b7b935b72fe94bc6adeabdbfdfbd6e2f-senior-specialist-major-gifts-national-immigration-law-center-los-angeles</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5afa137a0dd44ffdb604bee1a7556984-senior-specialist-major-gifts-national-immigration-law-center-washington</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4bc90d2e2f7143b292b28d70b660947f-senior-specialist-major-gifts-national-immigration-law-center-houston</t>
+  </si>
+  <si>
+    <t>Shareholder Advocate</t>
+  </si>
+  <si>
+    <t>The Public Interest Network</t>
+  </si>
+  <si>
+    <t>USD 41750.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a5c955d22e244919f7656f4036b4085-shareholder-advocate-the-public-interest-network-boston</t>
+  </si>
+  <si>
     <t>USD 92000.00 - 108000.00/year</t>
   </si>
   <si>
-    <t>Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/305fccda569b49f5b02b6925df8e7166-sr-conservation-manager-conservation-campaigns-the-wilderness-society-washington</t>
   </si>
   <si>
+    <t>Sr. Director, National Prison Programs</t>
+  </si>
+  <si>
+    <t>Defy Ventures</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1d9b819604f4618b112820e78333a75-sr-director-national-prison-programs-defy-ventures-los-angeles</t>
+  </si>
+  <si>
+    <t>Sr. Director, National Workforce and Reentry</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cba0ad1c6c5545a08087c6f15a97f472-sr-director-national-workforce-and-reentry-defy-ventures-los-angeles</t>
+  </si>
+  <si>
     <t>Staff Accountant</t>
   </si>
   <si>
@@ -1537,6 +2482,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/61722d22b6884a7da5fae04a73808814-staff-accountant-wesley-theological-seminary-washington</t>
   </si>
   <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union of Arkansas</t>
+  </si>
+  <si>
+    <t>Little Rock, Arkansas</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79a40012bdef47c4ad34a365834c6021-staff-attorney-american-civil-liberties-union-of-arkansas-little-rock</t>
+  </si>
+  <si>
     <t>Staff Attorney, Tenant Advocacy Program</t>
   </si>
   <si>
@@ -1555,6 +2515,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/5c5c4a508dc147d7bbbc841b17545fdb-staff-attorney-tenant-advocacy-program-catholic-migration-services-queens-county</t>
   </si>
   <si>
+    <t>State Conservation Advocate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/63d8f26ae82c4999af0ba357bc22b5a8-state-conservation-advocate-environment-america-boston</t>
+  </si>
+  <si>
+    <t>Supervising Attorney (Disaster Legal Services) – Pro Bono Workgroup</t>
+  </si>
+  <si>
+    <t>Legal Aid Foundation of Los Angeles</t>
+  </si>
+  <si>
+    <t>USD 105174.00 - 123039.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46b326f75c714446b4132b6e4e5f8e13-supervising-attorney-disaster-legal-services-pro-bono-workgroup-legal-aid-foundation-of-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Synagogue Receptionist / Administrative Assistant</t>
   </si>
   <si>
@@ -1594,6 +2572,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e3535c842baf4d9698f6bc30b9d21f51-unit-director-atp-geel-community-services-inc-the-bronx</t>
   </si>
   <si>
+    <t>Vice President of External Affairs</t>
+  </si>
+  <si>
+    <t>Chicago Foundation for Women</t>
+  </si>
+  <si>
+    <t>USD 162754.00 - 180838.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Philanthropy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43752a1e3b4c444b85a9024595c6dda2-vice-president-of-external-affairs-chicago-foundation-for-women-chicago</t>
+  </si>
+  <si>
     <t>Video Editor</t>
   </si>
   <si>
@@ -1634,6 +2627,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/4cfdf94ebdaa4869b9170acb0536251c-visitor-services-associate-fairfield-museum-and-history-center-fairfield</t>
+  </si>
+  <si>
+    <t>Waste is Out of Fashion Campaigner</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0bdcb484e404819b04c1962fbd1f554-waste-is-out-of-fashion-campaigner-us-pirg-portland</t>
   </si>
 </sst>
 </file>
@@ -2019,7 +3018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2615,42 +3614,42 @@
         <v>138</v>
       </c>
       <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
         <v>139</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>141</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" t="s">
         <v>143</v>
       </c>
-      <c r="B27" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" t="s">
         <v>144</v>
-      </c>
-      <c r="D27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" t="s">
-        <v>30</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>145</v>
@@ -2661,19 +3660,19 @@
         <v>146</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>147</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>148</v>
@@ -2684,45 +3683,68 @@
         <v>149</v>
       </c>
       <c r="B29" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>151</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F29" t="s">
-        <v>153</v>
+        <v>60</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
         <v>155</v>
       </c>
-      <c r="B30" t="s">
+      <c r="F30" t="s">
         <v>156</v>
       </c>
-      <c r="C30" t="s">
+      <c r="H30" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D30" t="s">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" t="s">
         <v>22</v>
       </c>
-      <c r="E30" t="s">
-        <v>158</v>
-      </c>
-      <c r="F30" t="s">
-        <v>159</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>160</v>
+      <c r="E31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F31" t="s">
+        <v>162</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2757,6 +3779,7 @@
     <hyperlink ref="H28" r:id="rId27"/>
     <hyperlink ref="H29" r:id="rId28"/>
     <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2765,7 +3788,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2806,54 +3829,77 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" t="s">
+        <v>176</v>
+      </c>
+      <c r="G4" t="s">
         <v>170</v>
       </c>
-      <c r="C3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>174</v>
+      <c r="H4" s="2" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2861,6 +3907,7 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2869,7 +3916,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2910,534 +3957,534 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F2" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C3" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D3" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="E5" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F5" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E6" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B7" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C7" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D7" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="E7" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F7" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="D8" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E8" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="F8" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="B9" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="D9" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E9" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="F9" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B10" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="D10" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E10" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F10" t="s">
-        <v>165</v>
+        <v>231</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B11" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D11" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E11" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="F11" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B12" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="D12" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E12" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="F12" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>242</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="C13" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E13" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="F13" t="s">
-        <v>233</v>
-      </c>
-      <c r="G13" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C14" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E14" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="F14" t="s">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C15" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E15" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="F15" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="B16" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="C16" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E16" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="F16" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>248</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
-        <v>237</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E17" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="F17" t="s">
-        <v>240</v>
+        <v>265</v>
+      </c>
+      <c r="G17" t="s">
+        <v>266</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="B18" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="C18" t="s">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="D18" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E18" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="F18" t="s">
-        <v>240</v>
+        <v>272</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="B19" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C19" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="D19" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E19" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="F19" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="C20" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="D20" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="E20" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="F20" t="s">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B21" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="C21" t="s">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c r="D21" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="F21" t="s">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B22" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="C22" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="D22" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E22" t="s">
-        <v>179</v>
+        <v>280</v>
       </c>
       <c r="F22" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>222</v>
       </c>
       <c r="C23" t="s">
-        <v>171</v>
+        <v>275</v>
       </c>
       <c r="D23" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E23" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="F23" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s">
-        <v>275</v>
+        <v>222</v>
       </c>
       <c r="C24" t="s">
-        <v>171</v>
+        <v>288</v>
       </c>
       <c r="D24" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E24" t="s">
-        <v>179</v>
+        <v>280</v>
       </c>
       <c r="F24" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -3445,88 +4492,88 @@
         <v>278</v>
       </c>
       <c r="B25" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="C25" t="s">
+        <v>290</v>
+      </c>
+      <c r="D25" t="s">
+        <v>186</v>
+      </c>
+      <c r="E25" t="s">
         <v>280</v>
       </c>
-      <c r="D25" t="s">
-        <v>178</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>281</v>
       </c>
-      <c r="F25" t="s">
-        <v>282</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>222</v>
       </c>
       <c r="C26" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="D26" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E26" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="F26" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B27" t="s">
-        <v>290</v>
+        <v>222</v>
       </c>
       <c r="C27" t="s">
-        <v>217</v>
+        <v>293</v>
       </c>
       <c r="D27" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E27" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="F27" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="C28" t="s">
-        <v>217</v>
+        <v>295</v>
       </c>
       <c r="D28" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="E28" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="F28" t="s">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>296</v>
@@ -3534,1178 +4581,3133 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>278</v>
+      </c>
+      <c r="B29" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" t="s">
+        <v>197</v>
+      </c>
+      <c r="D29" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" t="s">
+        <v>280</v>
+      </c>
+      <c r="F29" t="s">
+        <v>281</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="B29" t="s">
-        <v>298</v>
-      </c>
-      <c r="C29" t="s">
-        <v>280</v>
-      </c>
-      <c r="D29" t="s">
-        <v>178</v>
-      </c>
-      <c r="E29" t="s">
-        <v>299</v>
-      </c>
-      <c r="F29" t="s">
-        <v>300</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C30" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D30" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F30" t="s">
-        <v>268</v>
+        <v>168</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s">
-        <v>306</v>
+        <v>269</v>
       </c>
       <c r="C31" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="D31" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E31" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="F31" t="s">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
       <c r="C32" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
       <c r="D32" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E32" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="F32" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="C33" t="s">
-        <v>217</v>
+        <v>309</v>
       </c>
       <c r="D33" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="F33" t="s">
-        <v>180</v>
+        <v>311</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C34" t="s">
-        <v>322</v>
+        <v>244</v>
       </c>
       <c r="D34" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E34" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="F34" t="s">
-        <v>324</v>
+        <v>168</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="C35" t="s">
-        <v>208</v>
+        <v>279</v>
       </c>
       <c r="D35" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F35" t="s">
-        <v>329</v>
+        <v>168</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="C36" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E36" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="F36" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="C37" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="D37" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="F37" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s">
-        <v>342</v>
+        <v>269</v>
       </c>
       <c r="C38" t="s">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="D38" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>291</v>
+        <v>330</v>
       </c>
       <c r="F38" t="s">
-        <v>344</v>
+        <v>272</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="B39" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="C39" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="D39" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E39" t="s">
-        <v>223</v>
+        <v>333</v>
       </c>
       <c r="F39" t="s">
-        <v>229</v>
+        <v>272</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C40" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="D40" t="s">
-        <v>178</v>
+        <v>217</v>
       </c>
       <c r="E40" t="s">
-        <v>263</v>
+        <v>337</v>
       </c>
       <c r="F40" t="s">
-        <v>350</v>
+        <v>188</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="C41" t="s">
-        <v>354</v>
+        <v>244</v>
       </c>
       <c r="D41" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="E41" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="F41" t="s">
-        <v>356</v>
+        <v>188</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>62</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="C42" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="D42" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E42" t="s">
-        <v>360</v>
+        <v>187</v>
       </c>
       <c r="F42" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>347</v>
       </c>
       <c r="B43" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C43" t="s">
-        <v>364</v>
+        <v>180</v>
       </c>
       <c r="D43" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E43" t="s">
-        <v>365</v>
+        <v>337</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>281</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="C44" t="s">
-        <v>369</v>
+        <v>180</v>
       </c>
       <c r="D44" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E44" t="s">
-        <v>370</v>
+        <v>187</v>
       </c>
       <c r="F44" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="C45" t="s">
-        <v>375</v>
+        <v>290</v>
       </c>
       <c r="D45" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E45" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="F45" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="C46" t="s">
-        <v>381</v>
+        <v>244</v>
       </c>
       <c r="D46" t="s">
-        <v>259</v>
+        <v>186</v>
       </c>
       <c r="E46" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="F46" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="C47" t="s">
-        <v>387</v>
+        <v>244</v>
       </c>
       <c r="D47" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>388</v>
+        <v>366</v>
       </c>
       <c r="F47" t="s">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>391</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s">
-        <v>221</v>
+        <v>370</v>
       </c>
       <c r="C48" t="s">
-        <v>392</v>
+        <v>244</v>
       </c>
       <c r="D48" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E48" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="F48" t="s">
-        <v>229</v>
+        <v>372</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s">
-        <v>396</v>
+        <v>336</v>
       </c>
       <c r="C49" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" t="s">
         <v>217</v>
       </c>
-      <c r="D49" t="s">
-        <v>259</v>
-      </c>
       <c r="E49" t="s">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="F49" t="s">
-        <v>398</v>
+        <v>188</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>400</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="C50" t="s">
-        <v>202</v>
+        <v>379</v>
       </c>
       <c r="D50" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E50" t="s">
-        <v>402</v>
+        <v>380</v>
       </c>
       <c r="F50" t="s">
-        <v>403</v>
+        <v>381</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>404</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>405</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="C51" t="s">
-        <v>407</v>
+        <v>290</v>
       </c>
       <c r="D51" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E51" t="s">
-        <v>408</v>
+        <v>385</v>
       </c>
       <c r="F51" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>410</v>
+        <v>387</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>411</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s">
-        <v>406</v>
+        <v>343</v>
       </c>
       <c r="C52" t="s">
-        <v>412</v>
+        <v>344</v>
       </c>
       <c r="D52" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E52" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="F52" t="s">
-        <v>409</v>
+        <v>345</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>413</v>
+        <v>390</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="C53" t="s">
-        <v>416</v>
+        <v>244</v>
       </c>
       <c r="D53" t="s">
-        <v>259</v>
+        <v>217</v>
       </c>
       <c r="E53" t="s">
-        <v>417</v>
+        <v>392</v>
       </c>
       <c r="F53" t="s">
-        <v>418</v>
+        <v>393</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>419</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s">
-        <v>421</v>
+        <v>396</v>
       </c>
       <c r="C54" t="s">
-        <v>422</v>
+        <v>397</v>
       </c>
       <c r="D54" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
-        <v>423</v>
+        <v>398</v>
       </c>
       <c r="F54" t="s">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>425</v>
+        <v>400</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>426</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s">
-        <v>427</v>
+        <v>402</v>
       </c>
       <c r="C55" t="s">
-        <v>428</v>
+        <v>403</v>
       </c>
       <c r="D55" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="F55" t="s">
-        <v>430</v>
+        <v>405</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>431</v>
+        <v>406</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>432</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s">
-        <v>433</v>
+        <v>408</v>
       </c>
       <c r="C56" t="s">
-        <v>434</v>
+        <v>409</v>
       </c>
       <c r="D56" t="s">
-        <v>178</v>
+        <v>410</v>
       </c>
       <c r="E56" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="F56" t="s">
-        <v>436</v>
+        <v>168</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>437</v>
+        <v>412</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>438</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s">
-        <v>221</v>
+        <v>408</v>
       </c>
       <c r="C57" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="D57" t="s">
-        <v>178</v>
+        <v>410</v>
       </c>
       <c r="E57" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="F57" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="B58" t="s">
-        <v>221</v>
+        <v>416</v>
       </c>
       <c r="C58" t="s">
-        <v>227</v>
+        <v>293</v>
       </c>
       <c r="D58" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E58" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="F58" t="s">
-        <v>229</v>
+        <v>418</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="C59" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D59" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E59" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="F59" t="s">
-        <v>165</v>
+        <v>423</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>447</v>
+        <v>424</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="B60" t="s">
-        <v>449</v>
+        <v>426</v>
       </c>
       <c r="C60" t="s">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="D60" t="s">
-        <v>451</v>
+        <v>186</v>
       </c>
       <c r="E60" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="F60" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
       <c r="B61" t="s">
-        <v>456</v>
+        <v>431</v>
       </c>
       <c r="C61" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D61" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E61" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="F61" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="B62" t="s">
-        <v>461</v>
+        <v>336</v>
       </c>
       <c r="C62" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="D62" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E62" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="F62" t="s">
-        <v>377</v>
+        <v>188</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="B63" t="s">
-        <v>258</v>
+        <v>439</v>
       </c>
       <c r="C63" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="D63" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E63" t="s">
-        <v>263</v>
+        <v>440</v>
       </c>
       <c r="F63" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C64" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="D64" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E64" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="F64" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="B65" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C65" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="D65" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E65" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="F65" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="B66" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="C66" t="s">
-        <v>217</v>
+        <v>293</v>
       </c>
       <c r="D66" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E66" t="s">
-        <v>477</v>
+        <v>455</v>
       </c>
       <c r="F66" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="B67" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="C67" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="D67" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E67" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="F67" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>481</v>
+        <v>459</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="B68" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
       <c r="C68" t="s">
-        <v>171</v>
+        <v>460</v>
       </c>
       <c r="D68" t="s">
-        <v>451</v>
+        <v>186</v>
       </c>
       <c r="E68" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
       <c r="F68" t="s">
-        <v>485</v>
+        <v>456</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>486</v>
+        <v>461</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>487</v>
+        <v>462</v>
       </c>
       <c r="B69" t="s">
-        <v>488</v>
+        <v>463</v>
       </c>
       <c r="C69" t="s">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="D69" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E69" t="s">
-        <v>490</v>
+        <v>465</v>
       </c>
       <c r="F69" t="s">
-        <v>491</v>
+        <v>466</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="B70" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="C70" t="s">
-        <v>495</v>
+        <v>244</v>
       </c>
       <c r="D70" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E70" t="s">
-        <v>496</v>
+        <v>310</v>
       </c>
       <c r="F70" t="s">
-        <v>497</v>
+        <v>168</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>498</v>
+        <v>470</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>169</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s">
-        <v>170</v>
+        <v>472</v>
       </c>
       <c r="C71" t="s">
-        <v>171</v>
+        <v>458</v>
       </c>
       <c r="D71" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E71" t="s">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="F71" t="s">
-        <v>500</v>
-      </c>
-      <c r="G71" t="s">
-        <v>234</v>
+        <v>474</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>501</v>
+        <v>475</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>502</v>
+        <v>476</v>
       </c>
       <c r="B72" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="C72" t="s">
-        <v>231</v>
+        <v>478</v>
       </c>
       <c r="D72" t="s">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="E72" t="s">
-        <v>504</v>
+        <v>479</v>
       </c>
       <c r="F72" t="s">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s">
-        <v>508</v>
+        <v>483</v>
       </c>
       <c r="C73" t="s">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="D73" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E73" t="s">
-        <v>510</v>
+        <v>371</v>
       </c>
       <c r="F73" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="B74" t="s">
-        <v>514</v>
+        <v>253</v>
       </c>
       <c r="C74" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="D74" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E74" t="s">
-        <v>515</v>
+        <v>255</v>
       </c>
       <c r="F74" t="s">
-        <v>383</v>
+        <v>261</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>516</v>
+        <v>488</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="B75" t="s">
-        <v>518</v>
+        <v>490</v>
       </c>
       <c r="C75" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="D75" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E75" t="s">
-        <v>520</v>
+        <v>492</v>
       </c>
       <c r="F75" t="s">
-        <v>521</v>
+        <v>493</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>522</v>
+        <v>494</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>523</v>
+        <v>495</v>
       </c>
       <c r="B76" t="s">
-        <v>237</v>
+        <v>496</v>
       </c>
       <c r="C76" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="D76" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E76" t="s">
-        <v>524</v>
+        <v>340</v>
       </c>
       <c r="F76" t="s">
-        <v>240</v>
+        <v>497</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>525</v>
+        <v>498</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="B77" t="s">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="C77" t="s">
-        <v>528</v>
+        <v>325</v>
       </c>
       <c r="D77" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="E77" t="s">
-        <v>529</v>
+        <v>501</v>
       </c>
       <c r="F77" t="s">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>531</v>
+        <v>503</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>532</v>
+        <v>504</v>
       </c>
       <c r="B78" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C78" t="s">
-        <v>238</v>
+        <v>295</v>
       </c>
       <c r="D78" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="E78" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="F78" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>506</v>
+      </c>
+      <c r="B79" t="s">
+        <v>507</v>
+      </c>
+      <c r="C79" t="s">
+        <v>288</v>
+      </c>
+      <c r="D79" t="s">
+        <v>186</v>
+      </c>
+      <c r="E79" t="s">
+        <v>508</v>
+      </c>
+      <c r="F79" t="s">
+        <v>509</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>511</v>
+      </c>
+      <c r="B80" t="s">
+        <v>512</v>
+      </c>
+      <c r="C80" t="s">
+        <v>283</v>
+      </c>
+      <c r="D80" t="s">
+        <v>186</v>
+      </c>
+      <c r="E80" t="s">
+        <v>513</v>
+      </c>
+      <c r="F80" t="s">
+        <v>168</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>62</v>
+      </c>
+      <c r="B81" t="s">
+        <v>515</v>
+      </c>
+      <c r="C81" t="s">
+        <v>516</v>
+      </c>
+      <c r="D81" t="s">
+        <v>186</v>
+      </c>
+      <c r="E81" t="s">
+        <v>517</v>
+      </c>
+      <c r="F81" t="s">
+        <v>518</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>62</v>
+      </c>
+      <c r="B82" t="s">
+        <v>520</v>
+      </c>
+      <c r="C82" t="s">
+        <v>521</v>
+      </c>
+      <c r="D82" t="s">
+        <v>186</v>
+      </c>
+      <c r="E82" t="s">
+        <v>522</v>
+      </c>
+      <c r="F82" t="s">
+        <v>188</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" t="s">
+        <v>524</v>
+      </c>
+      <c r="C83" t="s">
+        <v>525</v>
+      </c>
+      <c r="D83" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83" t="s">
+        <v>526</v>
+      </c>
+      <c r="F83" t="s">
+        <v>527</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>529</v>
+      </c>
+      <c r="B84" t="s">
+        <v>318</v>
+      </c>
+      <c r="C84" t="s">
+        <v>229</v>
+      </c>
+      <c r="D84" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84" t="s">
+        <v>530</v>
+      </c>
+      <c r="F84" t="s">
+        <v>168</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>532</v>
+      </c>
+      <c r="B85" t="s">
+        <v>533</v>
+      </c>
+      <c r="C85" t="s">
         <v>534</v>
       </c>
-      <c r="B79" t="s">
+      <c r="D85" t="s">
+        <v>186</v>
+      </c>
+      <c r="E85" t="s">
         <v>535</v>
       </c>
-      <c r="C79" t="s">
+      <c r="F85" t="s">
         <v>536</v>
       </c>
-      <c r="D79" t="s">
+      <c r="H85" s="2" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>538</v>
+      </c>
+      <c r="B86" t="s">
+        <v>539</v>
+      </c>
+      <c r="C86" t="s">
+        <v>540</v>
+      </c>
+      <c r="D86" t="s">
+        <v>186</v>
+      </c>
+      <c r="E86" t="s">
+        <v>541</v>
+      </c>
+      <c r="F86" t="s">
+        <v>542</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>544</v>
+      </c>
+      <c r="B87" t="s">
+        <v>545</v>
+      </c>
+      <c r="C87" t="s">
+        <v>546</v>
+      </c>
+      <c r="D87" t="s">
+        <v>217</v>
+      </c>
+      <c r="E87" t="s">
+        <v>547</v>
+      </c>
+      <c r="F87" t="s">
+        <v>548</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>550</v>
+      </c>
+      <c r="B88" t="s">
+        <v>551</v>
+      </c>
+      <c r="C88" t="s">
+        <v>552</v>
+      </c>
+      <c r="D88" t="s">
+        <v>186</v>
+      </c>
+      <c r="E88" t="s">
+        <v>553</v>
+      </c>
+      <c r="F88" t="s">
+        <v>554</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>556</v>
+      </c>
+      <c r="B89" t="s">
+        <v>222</v>
+      </c>
+      <c r="C89" t="s">
+        <v>229</v>
+      </c>
+      <c r="D89" t="s">
+        <v>186</v>
+      </c>
+      <c r="E89" t="s">
+        <v>224</v>
+      </c>
+      <c r="F89" t="s">
+        <v>225</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>558</v>
+      </c>
+      <c r="B90" t="s">
+        <v>559</v>
+      </c>
+      <c r="C90" t="s">
+        <v>560</v>
+      </c>
+      <c r="D90" t="s">
+        <v>186</v>
+      </c>
+      <c r="E90" t="s">
+        <v>561</v>
+      </c>
+      <c r="F90" t="s">
+        <v>168</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>563</v>
+      </c>
+      <c r="B91" t="s">
+        <v>253</v>
+      </c>
+      <c r="C91" t="s">
+        <v>564</v>
+      </c>
+      <c r="D91" t="s">
+        <v>186</v>
+      </c>
+      <c r="E91" t="s">
+        <v>565</v>
+      </c>
+      <c r="F91" t="s">
+        <v>261</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>567</v>
+      </c>
+      <c r="B92" t="s">
+        <v>568</v>
+      </c>
+      <c r="C92" t="s">
+        <v>244</v>
+      </c>
+      <c r="D92" t="s">
+        <v>217</v>
+      </c>
+      <c r="E92" t="s">
+        <v>569</v>
+      </c>
+      <c r="F92" t="s">
+        <v>570</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>572</v>
+      </c>
+      <c r="B93" t="s">
+        <v>573</v>
+      </c>
+      <c r="C93" t="s">
+        <v>574</v>
+      </c>
+      <c r="D93" t="s">
+        <v>186</v>
+      </c>
+      <c r="E93" t="s">
+        <v>575</v>
+      </c>
+      <c r="F93" t="s">
+        <v>576</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>578</v>
+      </c>
+      <c r="B94" t="s">
+        <v>579</v>
+      </c>
+      <c r="C94" t="s">
+        <v>229</v>
+      </c>
+      <c r="D94" t="s">
+        <v>186</v>
+      </c>
+      <c r="E94" t="s">
+        <v>580</v>
+      </c>
+      <c r="F94" t="s">
+        <v>581</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>583</v>
+      </c>
+      <c r="B95" t="s">
+        <v>584</v>
+      </c>
+      <c r="C95" t="s">
+        <v>585</v>
+      </c>
+      <c r="D95" t="s">
+        <v>186</v>
+      </c>
+      <c r="E95" t="s">
+        <v>586</v>
+      </c>
+      <c r="F95" t="s">
+        <v>587</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>589</v>
+      </c>
+      <c r="B96" t="s">
+        <v>431</v>
+      </c>
+      <c r="C96" t="s">
+        <v>235</v>
+      </c>
+      <c r="D96" t="s">
+        <v>186</v>
+      </c>
+      <c r="E96" t="s">
+        <v>590</v>
+      </c>
+      <c r="F96" t="s">
+        <v>591</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>593</v>
+      </c>
+      <c r="B97" t="s">
+        <v>431</v>
+      </c>
+      <c r="C97" t="s">
+        <v>235</v>
+      </c>
+      <c r="D97" t="s">
+        <v>186</v>
+      </c>
+      <c r="E97" t="s">
+        <v>450</v>
+      </c>
+      <c r="F97" t="s">
+        <v>591</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>595</v>
+      </c>
+      <c r="B98" t="s">
+        <v>596</v>
+      </c>
+      <c r="C98" t="s">
+        <v>597</v>
+      </c>
+      <c r="D98" t="s">
+        <v>204</v>
+      </c>
+      <c r="E98" t="s">
+        <v>598</v>
+      </c>
+      <c r="F98" t="s">
+        <v>599</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>601</v>
+      </c>
+      <c r="B99" t="s">
+        <v>602</v>
+      </c>
+      <c r="C99" t="s">
+        <v>603</v>
+      </c>
+      <c r="D99" t="s">
+        <v>186</v>
+      </c>
+      <c r="E99" t="s">
+        <v>604</v>
+      </c>
+      <c r="F99" t="s">
+        <v>605</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>607</v>
+      </c>
+      <c r="B100" t="s">
+        <v>602</v>
+      </c>
+      <c r="C100" t="s">
+        <v>603</v>
+      </c>
+      <c r="D100" t="s">
+        <v>186</v>
+      </c>
+      <c r="E100" t="s">
+        <v>608</v>
+      </c>
+      <c r="F100" t="s">
+        <v>605</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>610</v>
+      </c>
+      <c r="B101" t="s">
+        <v>611</v>
+      </c>
+      <c r="C101" t="s">
+        <v>612</v>
+      </c>
+      <c r="D101" t="s">
+        <v>186</v>
+      </c>
+      <c r="E101" t="s">
+        <v>613</v>
+      </c>
+      <c r="F101" t="s">
+        <v>614</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>616</v>
+      </c>
+      <c r="B102" t="s">
+        <v>611</v>
+      </c>
+      <c r="C102" t="s">
+        <v>617</v>
+      </c>
+      <c r="D102" t="s">
+        <v>186</v>
+      </c>
+      <c r="E102" t="s">
+        <v>613</v>
+      </c>
+      <c r="F102" t="s">
+        <v>614</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>619</v>
+      </c>
+      <c r="B103" t="s">
+        <v>620</v>
+      </c>
+      <c r="C103" t="s">
+        <v>621</v>
+      </c>
+      <c r="D103" t="s">
+        <v>217</v>
+      </c>
+      <c r="E103" t="s">
+        <v>622</v>
+      </c>
+      <c r="F103" t="s">
+        <v>623</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>625</v>
+      </c>
+      <c r="B104" t="s">
+        <v>626</v>
+      </c>
+      <c r="C104" t="s">
+        <v>627</v>
+      </c>
+      <c r="D104" t="s">
+        <v>186</v>
+      </c>
+      <c r="E104" t="s">
+        <v>628</v>
+      </c>
+      <c r="F104" t="s">
+        <v>629</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>625</v>
+      </c>
+      <c r="B105" t="s">
+        <v>631</v>
+      </c>
+      <c r="C105" t="s">
+        <v>235</v>
+      </c>
+      <c r="D105" t="s">
+        <v>186</v>
+      </c>
+      <c r="E105" t="s">
+        <v>632</v>
+      </c>
+      <c r="F105" t="s">
+        <v>633</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>635</v>
+      </c>
+      <c r="B106" t="s">
+        <v>507</v>
+      </c>
+      <c r="C106" t="s">
+        <v>288</v>
+      </c>
+      <c r="D106" t="s">
+        <v>186</v>
+      </c>
+      <c r="E106" t="s">
+        <v>636</v>
+      </c>
+      <c r="F106" t="s">
+        <v>509</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>638</v>
+      </c>
+      <c r="B107" t="s">
+        <v>639</v>
+      </c>
+      <c r="C107" t="s">
+        <v>640</v>
+      </c>
+      <c r="D107" t="s">
+        <v>186</v>
+      </c>
+      <c r="E107" t="s">
+        <v>641</v>
+      </c>
+      <c r="F107" t="s">
+        <v>642</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>644</v>
+      </c>
+      <c r="B108" t="s">
+        <v>645</v>
+      </c>
+      <c r="C108" t="s">
+        <v>290</v>
+      </c>
+      <c r="D108" t="s">
+        <v>217</v>
+      </c>
+      <c r="E108" t="s">
+        <v>646</v>
+      </c>
+      <c r="F108" t="s">
+        <v>647</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>649</v>
+      </c>
+      <c r="B109" t="s">
+        <v>650</v>
+      </c>
+      <c r="C109" t="s">
+        <v>283</v>
+      </c>
+      <c r="D109" t="s">
+        <v>217</v>
+      </c>
+      <c r="E109" t="s">
+        <v>651</v>
+      </c>
+      <c r="F109" t="s">
+        <v>240</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>653</v>
+      </c>
+      <c r="B110" t="s">
+        <v>654</v>
+      </c>
+      <c r="C110" t="s">
+        <v>655</v>
+      </c>
+      <c r="D110" t="s">
+        <v>186</v>
+      </c>
+      <c r="E110" t="s">
+        <v>656</v>
+      </c>
+      <c r="F110" t="s">
+        <v>657</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>659</v>
+      </c>
+      <c r="B111" t="s">
+        <v>253</v>
+      </c>
+      <c r="C111" t="s">
+        <v>660</v>
+      </c>
+      <c r="D111" t="s">
+        <v>186</v>
+      </c>
+      <c r="E111" t="s">
+        <v>661</v>
+      </c>
+      <c r="F111" t="s">
+        <v>261</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>659</v>
+      </c>
+      <c r="B112" t="s">
+        <v>253</v>
+      </c>
+      <c r="C112" t="s">
+        <v>259</v>
+      </c>
+      <c r="D112" t="s">
+        <v>186</v>
+      </c>
+      <c r="E112" t="s">
+        <v>663</v>
+      </c>
+      <c r="F112" t="s">
+        <v>261</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>665</v>
+      </c>
+      <c r="B113" t="s">
+        <v>666</v>
+      </c>
+      <c r="C113" t="s">
+        <v>244</v>
+      </c>
+      <c r="D113" t="s">
+        <v>186</v>
+      </c>
+      <c r="E113" t="s">
+        <v>667</v>
+      </c>
+      <c r="F113" t="s">
+        <v>168</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>669</v>
+      </c>
+      <c r="B114" t="s">
+        <v>670</v>
+      </c>
+      <c r="C114" t="s">
+        <v>229</v>
+      </c>
+      <c r="D114" t="s">
+        <v>186</v>
+      </c>
+      <c r="E114" t="s">
+        <v>671</v>
+      </c>
+      <c r="F114" t="s">
+        <v>168</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>673</v>
+      </c>
+      <c r="B115" t="s">
+        <v>674</v>
+      </c>
+      <c r="C115" t="s">
+        <v>675</v>
+      </c>
+      <c r="D115" t="s">
+        <v>410</v>
+      </c>
+      <c r="E115" t="s">
+        <v>676</v>
+      </c>
+      <c r="F115" t="s">
+        <v>677</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>679</v>
+      </c>
+      <c r="B116" t="s">
+        <v>680</v>
+      </c>
+      <c r="C116" t="s">
+        <v>229</v>
+      </c>
+      <c r="D116" t="s">
+        <v>186</v>
+      </c>
+      <c r="E116" t="s">
+        <v>681</v>
+      </c>
+      <c r="F116" t="s">
+        <v>682</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>684</v>
+      </c>
+      <c r="B117" t="s">
+        <v>685</v>
+      </c>
+      <c r="C117" t="s">
+        <v>293</v>
+      </c>
+      <c r="D117" t="s">
+        <v>186</v>
+      </c>
+      <c r="E117" t="s">
+        <v>686</v>
+      </c>
+      <c r="F117" t="s">
+        <v>687</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>684</v>
+      </c>
+      <c r="B118" t="s">
+        <v>685</v>
+      </c>
+      <c r="C118" t="s">
+        <v>460</v>
+      </c>
+      <c r="D118" t="s">
+        <v>186</v>
+      </c>
+      <c r="E118" t="s">
+        <v>686</v>
+      </c>
+      <c r="F118" t="s">
+        <v>687</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>684</v>
+      </c>
+      <c r="B119" t="s">
+        <v>685</v>
+      </c>
+      <c r="C119" t="s">
+        <v>690</v>
+      </c>
+      <c r="D119" t="s">
+        <v>186</v>
+      </c>
+      <c r="E119" t="s">
+        <v>686</v>
+      </c>
+      <c r="F119" t="s">
+        <v>687</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>692</v>
+      </c>
+      <c r="B120" t="s">
+        <v>693</v>
+      </c>
+      <c r="C120" t="s">
+        <v>244</v>
+      </c>
+      <c r="D120" t="s">
+        <v>410</v>
+      </c>
+      <c r="E120" t="s">
+        <v>694</v>
+      </c>
+      <c r="F120" t="s">
+        <v>695</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>697</v>
+      </c>
+      <c r="B121" t="s">
+        <v>222</v>
+      </c>
+      <c r="C121" t="s">
+        <v>293</v>
+      </c>
+      <c r="D121" t="s">
+        <v>186</v>
+      </c>
+      <c r="E121" t="s">
+        <v>224</v>
+      </c>
+      <c r="F121" t="s">
+        <v>225</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>699</v>
+      </c>
+      <c r="B122" t="s">
+        <v>700</v>
+      </c>
+      <c r="C122" t="s">
+        <v>701</v>
+      </c>
+      <c r="D122" t="s">
+        <v>186</v>
+      </c>
+      <c r="E122" t="s">
+        <v>702</v>
+      </c>
+      <c r="F122" t="s">
+        <v>168</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>704</v>
+      </c>
+      <c r="B123" t="s">
+        <v>705</v>
+      </c>
+      <c r="C123" t="s">
+        <v>413</v>
+      </c>
+      <c r="D123" t="s">
+        <v>186</v>
+      </c>
+      <c r="E123" t="s">
+        <v>404</v>
+      </c>
+      <c r="F123" t="s">
+        <v>168</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>707</v>
+      </c>
+      <c r="B124" t="s">
+        <v>708</v>
+      </c>
+      <c r="C124" t="s">
+        <v>244</v>
+      </c>
+      <c r="D124" t="s">
+        <v>186</v>
+      </c>
+      <c r="E124" t="s">
+        <v>709</v>
+      </c>
+      <c r="F124" t="s">
+        <v>710</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>712</v>
+      </c>
+      <c r="B125" t="s">
+        <v>713</v>
+      </c>
+      <c r="C125" t="s">
+        <v>244</v>
+      </c>
+      <c r="D125" t="s">
+        <v>186</v>
+      </c>
+      <c r="E125" t="s">
+        <v>709</v>
+      </c>
+      <c r="F125" t="s">
+        <v>542</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>712</v>
+      </c>
+      <c r="B126" t="s">
+        <v>715</v>
+      </c>
+      <c r="C126" t="s">
+        <v>716</v>
+      </c>
+      <c r="D126" t="s">
+        <v>410</v>
+      </c>
+      <c r="E126" t="s">
+        <v>337</v>
+      </c>
+      <c r="F126" t="s">
+        <v>717</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>719</v>
+      </c>
+      <c r="B127" t="s">
+        <v>336</v>
+      </c>
+      <c r="C127" t="s">
+        <v>244</v>
+      </c>
+      <c r="D127" t="s">
+        <v>186</v>
+      </c>
+      <c r="E127" t="s">
+        <v>340</v>
+      </c>
+      <c r="F127" t="s">
+        <v>188</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>721</v>
+      </c>
+      <c r="B128" t="s">
+        <v>722</v>
+      </c>
+      <c r="C128" t="s">
+        <v>723</v>
+      </c>
+      <c r="D128" t="s">
+        <v>186</v>
+      </c>
+      <c r="E128" t="s">
+        <v>724</v>
+      </c>
+      <c r="F128" t="s">
+        <v>725</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>727</v>
+      </c>
+      <c r="B129" t="s">
+        <v>728</v>
+      </c>
+      <c r="C129" t="s">
+        <v>229</v>
+      </c>
+      <c r="D129" t="s">
+        <v>186</v>
+      </c>
+      <c r="E129" t="s">
+        <v>729</v>
+      </c>
+      <c r="F129" t="s">
+        <v>730</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>727</v>
+      </c>
+      <c r="B130" t="s">
+        <v>728</v>
+      </c>
+      <c r="C130" t="s">
+        <v>244</v>
+      </c>
+      <c r="D130" t="s">
+        <v>186</v>
+      </c>
+      <c r="E130" t="s">
+        <v>732</v>
+      </c>
+      <c r="F130" t="s">
+        <v>730</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>727</v>
+      </c>
+      <c r="B131" t="s">
+        <v>728</v>
+      </c>
+      <c r="C131" t="s">
+        <v>734</v>
+      </c>
+      <c r="D131" t="s">
+        <v>186</v>
+      </c>
+      <c r="E131" t="s">
+        <v>735</v>
+      </c>
+      <c r="F131" t="s">
+        <v>730</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>737</v>
+      </c>
+      <c r="B132" t="s">
+        <v>738</v>
+      </c>
+      <c r="C132" t="s">
+        <v>263</v>
+      </c>
+      <c r="D132" t="s">
+        <v>186</v>
+      </c>
+      <c r="E132" t="s">
+        <v>739</v>
+      </c>
+      <c r="F132" t="s">
+        <v>740</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>742</v>
+      </c>
+      <c r="B133" t="s">
+        <v>743</v>
+      </c>
+      <c r="C133" t="s">
+        <v>180</v>
+      </c>
+      <c r="D133" t="s">
+        <v>186</v>
+      </c>
+      <c r="E133" t="s">
+        <v>744</v>
+      </c>
+      <c r="F133" t="s">
+        <v>745</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>747</v>
+      </c>
+      <c r="B134" t="s">
+        <v>748</v>
+      </c>
+      <c r="C134" t="s">
+        <v>180</v>
+      </c>
+      <c r="D134" t="s">
+        <v>410</v>
+      </c>
+      <c r="E134" t="s">
+        <v>749</v>
+      </c>
+      <c r="F134" t="s">
+        <v>750</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>752</v>
+      </c>
+      <c r="B135" t="s">
+        <v>507</v>
+      </c>
+      <c r="C135" t="s">
+        <v>288</v>
+      </c>
+      <c r="D135" t="s">
+        <v>186</v>
+      </c>
+      <c r="E135" t="s">
+        <v>753</v>
+      </c>
+      <c r="F135" t="s">
+        <v>509</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>755</v>
+      </c>
+      <c r="B136" t="s">
+        <v>756</v>
+      </c>
+      <c r="C136" t="s">
+        <v>464</v>
+      </c>
+      <c r="D136" t="s">
+        <v>186</v>
+      </c>
+      <c r="E136" t="s">
+        <v>757</v>
+      </c>
+      <c r="F136" t="s">
+        <v>758</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>760</v>
+      </c>
+      <c r="B137" t="s">
+        <v>761</v>
+      </c>
+      <c r="C137" t="s">
+        <v>279</v>
+      </c>
+      <c r="D137" t="s">
+        <v>186</v>
+      </c>
+      <c r="E137" t="s">
+        <v>667</v>
+      </c>
+      <c r="F137" t="s">
+        <v>762</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>764</v>
+      </c>
+      <c r="B138" t="s">
+        <v>765</v>
+      </c>
+      <c r="C138" t="s">
+        <v>279</v>
+      </c>
+      <c r="D138" t="s">
+        <v>186</v>
+      </c>
+      <c r="E138" t="s">
+        <v>766</v>
+      </c>
+      <c r="F138" t="s">
+        <v>633</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>768</v>
+      </c>
+      <c r="B139" t="s">
+        <v>769</v>
+      </c>
+      <c r="C139" t="s">
+        <v>770</v>
+      </c>
+      <c r="D139" t="s">
+        <v>186</v>
+      </c>
+      <c r="E139" t="s">
+        <v>771</v>
+      </c>
+      <c r="F139" t="s">
+        <v>168</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>773</v>
+      </c>
+      <c r="B140" t="s">
+        <v>774</v>
+      </c>
+      <c r="C140" t="s">
+        <v>775</v>
+      </c>
+      <c r="D140" t="s">
+        <v>186</v>
+      </c>
+      <c r="E140" t="s">
+        <v>776</v>
+      </c>
+      <c r="F140" t="s">
+        <v>777</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>779</v>
+      </c>
+      <c r="B141" t="s">
+        <v>780</v>
+      </c>
+      <c r="C141" t="s">
+        <v>244</v>
+      </c>
+      <c r="D141" t="s">
+        <v>186</v>
+      </c>
+      <c r="E141" t="s">
+        <v>781</v>
+      </c>
+      <c r="F141" t="s">
+        <v>782</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>784</v>
+      </c>
+      <c r="B142" t="s">
+        <v>785</v>
+      </c>
+      <c r="C142" t="s">
+        <v>786</v>
+      </c>
+      <c r="D142" t="s">
+        <v>186</v>
+      </c>
+      <c r="E142" t="s">
+        <v>787</v>
+      </c>
+      <c r="F142" t="s">
+        <v>788</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>790</v>
+      </c>
+      <c r="B143" t="s">
+        <v>791</v>
+      </c>
+      <c r="C143" t="s">
+        <v>792</v>
+      </c>
+      <c r="D143" t="s">
+        <v>186</v>
+      </c>
+      <c r="E143" t="s">
+        <v>793</v>
+      </c>
+      <c r="F143" t="s">
+        <v>794</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>796</v>
+      </c>
+      <c r="B144" t="s">
+        <v>797</v>
+      </c>
+      <c r="C144" t="s">
+        <v>180</v>
+      </c>
+      <c r="D144" t="s">
+        <v>186</v>
+      </c>
+      <c r="E144" t="s">
+        <v>798</v>
+      </c>
+      <c r="F144" t="s">
+        <v>799</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>796</v>
+      </c>
+      <c r="B145" t="s">
+        <v>797</v>
+      </c>
+      <c r="C145" t="s">
+        <v>180</v>
+      </c>
+      <c r="D145" t="s">
+        <v>186</v>
+      </c>
+      <c r="E145" t="s">
+        <v>168</v>
+      </c>
+      <c r="F145" t="s">
+        <v>799</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>796</v>
+      </c>
+      <c r="B146" t="s">
+        <v>797</v>
+      </c>
+      <c r="C146" t="s">
+        <v>180</v>
+      </c>
+      <c r="D146" t="s">
+        <v>186</v>
+      </c>
+      <c r="E146" t="s">
+        <v>798</v>
+      </c>
+      <c r="F146" t="s">
+        <v>799</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>796</v>
+      </c>
+      <c r="B147" t="s">
+        <v>797</v>
+      </c>
+      <c r="C147" t="s">
+        <v>180</v>
+      </c>
+      <c r="D147" t="s">
+        <v>186</v>
+      </c>
+      <c r="E147" t="s">
+        <v>798</v>
+      </c>
+      <c r="F147" t="s">
+        <v>799</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>804</v>
+      </c>
+      <c r="B148" t="s">
+        <v>805</v>
+      </c>
+      <c r="C148" t="s">
+        <v>290</v>
+      </c>
+      <c r="D148" t="s">
+        <v>186</v>
+      </c>
+      <c r="E148" t="s">
+        <v>806</v>
+      </c>
+      <c r="F148" t="s">
+        <v>225</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
         <v>178</v>
       </c>
-      <c r="E79" t="s">
-        <v>537</v>
-      </c>
-      <c r="F79" t="s">
-        <v>538</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>539</v>
+      <c r="B149" t="s">
+        <v>179</v>
+      </c>
+      <c r="C149" t="s">
+        <v>180</v>
+      </c>
+      <c r="D149" t="s">
+        <v>186</v>
+      </c>
+      <c r="E149" t="s">
+        <v>808</v>
+      </c>
+      <c r="F149" t="s">
+        <v>225</v>
+      </c>
+      <c r="G149" t="s">
+        <v>266</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>810</v>
+      </c>
+      <c r="B150" t="s">
+        <v>811</v>
+      </c>
+      <c r="C150" t="s">
+        <v>180</v>
+      </c>
+      <c r="D150" t="s">
+        <v>186</v>
+      </c>
+      <c r="E150" t="s">
+        <v>812</v>
+      </c>
+      <c r="F150" t="s">
+        <v>813</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>815</v>
+      </c>
+      <c r="B151" t="s">
+        <v>811</v>
+      </c>
+      <c r="C151" t="s">
+        <v>180</v>
+      </c>
+      <c r="D151" t="s">
+        <v>186</v>
+      </c>
+      <c r="E151" t="s">
+        <v>812</v>
+      </c>
+      <c r="F151" t="s">
+        <v>813</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>817</v>
+      </c>
+      <c r="B152" t="s">
+        <v>818</v>
+      </c>
+      <c r="C152" t="s">
+        <v>263</v>
+      </c>
+      <c r="D152" t="s">
+        <v>186</v>
+      </c>
+      <c r="E152" t="s">
+        <v>819</v>
+      </c>
+      <c r="F152" t="s">
+        <v>820</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>822</v>
+      </c>
+      <c r="B153" t="s">
+        <v>823</v>
+      </c>
+      <c r="C153" t="s">
+        <v>824</v>
+      </c>
+      <c r="D153" t="s">
+        <v>186</v>
+      </c>
+      <c r="E153" t="s">
+        <v>825</v>
+      </c>
+      <c r="F153" t="s">
+        <v>493</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>827</v>
+      </c>
+      <c r="B154" t="s">
+        <v>828</v>
+      </c>
+      <c r="C154" t="s">
+        <v>829</v>
+      </c>
+      <c r="D154" t="s">
+        <v>186</v>
+      </c>
+      <c r="E154" t="s">
+        <v>830</v>
+      </c>
+      <c r="F154" t="s">
+        <v>831</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>833</v>
+      </c>
+      <c r="B155" t="s">
+        <v>222</v>
+      </c>
+      <c r="C155" t="s">
+        <v>290</v>
+      </c>
+      <c r="D155" t="s">
+        <v>186</v>
+      </c>
+      <c r="E155" t="s">
+        <v>806</v>
+      </c>
+      <c r="F155" t="s">
+        <v>225</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>835</v>
+      </c>
+      <c r="B156" t="s">
+        <v>836</v>
+      </c>
+      <c r="C156" t="s">
+        <v>325</v>
+      </c>
+      <c r="D156" t="s">
+        <v>186</v>
+      </c>
+      <c r="E156" t="s">
+        <v>837</v>
+      </c>
+      <c r="F156" t="s">
+        <v>423</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>839</v>
+      </c>
+      <c r="B157" t="s">
+        <v>840</v>
+      </c>
+      <c r="C157" t="s">
+        <v>235</v>
+      </c>
+      <c r="D157" t="s">
+        <v>186</v>
+      </c>
+      <c r="E157" t="s">
+        <v>841</v>
+      </c>
+      <c r="F157" t="s">
+        <v>548</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>843</v>
+      </c>
+      <c r="B158" t="s">
+        <v>844</v>
+      </c>
+      <c r="C158" t="s">
+        <v>845</v>
+      </c>
+      <c r="D158" t="s">
+        <v>186</v>
+      </c>
+      <c r="E158" t="s">
+        <v>846</v>
+      </c>
+      <c r="F158" t="s">
+        <v>847</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>849</v>
+      </c>
+      <c r="B159" t="s">
+        <v>269</v>
+      </c>
+      <c r="C159" t="s">
+        <v>270</v>
+      </c>
+      <c r="D159" t="s">
+        <v>186</v>
+      </c>
+      <c r="E159" t="s">
+        <v>850</v>
+      </c>
+      <c r="F159" t="s">
+        <v>272</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>852</v>
+      </c>
+      <c r="B160" t="s">
+        <v>853</v>
+      </c>
+      <c r="C160" t="s">
+        <v>279</v>
+      </c>
+      <c r="D160" t="s">
+        <v>186</v>
+      </c>
+      <c r="E160" t="s">
+        <v>854</v>
+      </c>
+      <c r="F160" t="s">
+        <v>855</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>857</v>
+      </c>
+      <c r="B161" t="s">
+        <v>858</v>
+      </c>
+      <c r="C161" t="s">
+        <v>859</v>
+      </c>
+      <c r="D161" t="s">
+        <v>192</v>
+      </c>
+      <c r="E161" t="s">
+        <v>860</v>
+      </c>
+      <c r="F161" t="s">
+        <v>861</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>863</v>
+      </c>
+      <c r="B162" t="s">
+        <v>269</v>
+      </c>
+      <c r="C162" t="s">
+        <v>270</v>
+      </c>
+      <c r="D162" t="s">
+        <v>186</v>
+      </c>
+      <c r="E162" t="s">
+        <v>211</v>
+      </c>
+      <c r="F162" t="s">
+        <v>272</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>865</v>
+      </c>
+      <c r="B163" t="s">
+        <v>866</v>
+      </c>
+      <c r="C163" t="s">
+        <v>867</v>
+      </c>
+      <c r="D163" t="s">
+        <v>186</v>
+      </c>
+      <c r="E163" t="s">
+        <v>868</v>
+      </c>
+      <c r="F163" t="s">
+        <v>869</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>871</v>
+      </c>
+      <c r="B164" t="s">
+        <v>454</v>
+      </c>
+      <c r="C164" t="s">
+        <v>295</v>
+      </c>
+      <c r="D164" t="s">
+        <v>186</v>
+      </c>
+      <c r="E164" t="s">
+        <v>224</v>
+      </c>
+      <c r="F164" t="s">
+        <v>225</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>872</v>
       </c>
     </row>
   </sheetData>
@@ -4789,6 +7791,91 @@
     <hyperlink ref="H77" r:id="rId76"/>
     <hyperlink ref="H78" r:id="rId77"/>
     <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
+    <hyperlink ref="H143" r:id="rId142"/>
+    <hyperlink ref="H144" r:id="rId143"/>
+    <hyperlink ref="H145" r:id="rId144"/>
+    <hyperlink ref="H146" r:id="rId145"/>
+    <hyperlink ref="H147" r:id="rId146"/>
+    <hyperlink ref="H148" r:id="rId147"/>
+    <hyperlink ref="H149" r:id="rId148"/>
+    <hyperlink ref="H150" r:id="rId149"/>
+    <hyperlink ref="H151" r:id="rId150"/>
+    <hyperlink ref="H152" r:id="rId151"/>
+    <hyperlink ref="H153" r:id="rId152"/>
+    <hyperlink ref="H154" r:id="rId153"/>
+    <hyperlink ref="H155" r:id="rId154"/>
+    <hyperlink ref="H156" r:id="rId155"/>
+    <hyperlink ref="H157" r:id="rId156"/>
+    <hyperlink ref="H158" r:id="rId157"/>
+    <hyperlink ref="H159" r:id="rId158"/>
+    <hyperlink ref="H160" r:id="rId159"/>
+    <hyperlink ref="H161" r:id="rId160"/>
+    <hyperlink ref="H162" r:id="rId161"/>
+    <hyperlink ref="H163" r:id="rId162"/>
+    <hyperlink ref="H164" r:id="rId163"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
